--- a/JsonConverter/ExcelFiles/WaveData.xlsx
+++ b/JsonConverter/ExcelFiles/WaveData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A43D9184-6728-49F1-A70D-731A61B1CAE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152788E9-93B2-447F-B92E-724BF89B1BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4740" yWindow="105" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="82">
   <si>
     <t>Id</t>
   </si>
@@ -167,6 +167,160 @@
   </si>
   <si>
     <t>float</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave_Chapter02_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave_Chapter02_02</t>
+  </si>
+  <si>
+    <t>Wave_Chapter02_03</t>
+  </si>
+  <si>
+    <t>Wave_Chapter02_04</t>
+  </si>
+  <si>
+    <t>Wave_Chapter02_05</t>
+  </si>
+  <si>
+    <t>Wave_Chapter02_06</t>
+  </si>
+  <si>
+    <t>Wave_Chapter02_07</t>
+  </si>
+  <si>
+    <t>Wave_Chapter02_08</t>
+  </si>
+  <si>
+    <t>Wave_Chapter02_09</t>
+  </si>
+  <si>
+    <t>Wave_Chapter02_10</t>
+  </si>
+  <si>
+    <t>Wave_Chapter02_11</t>
+  </si>
+  <si>
+    <t>Wave_Chapter02_12</t>
+  </si>
+  <si>
+    <t>Wave_Chapter02_13</t>
+  </si>
+  <si>
+    <t>Wave_Chapter02_14</t>
+  </si>
+  <si>
+    <t>Wave_Chapter02_15</t>
+  </si>
+  <si>
+    <t>Wave_Chapter03_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave_Chapter03_02</t>
+  </si>
+  <si>
+    <t>Wave_Chapter03_03</t>
+  </si>
+  <si>
+    <t>Wave_Chapter03_04</t>
+  </si>
+  <si>
+    <t>Wave_Chapter03_05</t>
+  </si>
+  <si>
+    <t>Wave_Chapter03_06</t>
+  </si>
+  <si>
+    <t>Wave_Chapter03_07</t>
+  </si>
+  <si>
+    <t>Wave_Chapter03_08</t>
+  </si>
+  <si>
+    <t>Wave_Chapter03_09</t>
+  </si>
+  <si>
+    <t>Wave_Chapter03_10</t>
+  </si>
+  <si>
+    <t>Wave_Chapter03_11</t>
+  </si>
+  <si>
+    <t>Wave_Chapter03_12</t>
+  </si>
+  <si>
+    <t>Wave_Chapter03_13</t>
+  </si>
+  <si>
+    <t>Wave_Chapter03_14</t>
+  </si>
+  <si>
+    <t>Wave_Chapter03_15</t>
+  </si>
+  <si>
+    <t>Wave_Chapter04_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave_Chapter04_02</t>
+  </si>
+  <si>
+    <t>Wave_Chapter04_03</t>
+  </si>
+  <si>
+    <t>Wave_Chapter04_04</t>
+  </si>
+  <si>
+    <t>Wave_Chapter04_05</t>
+  </si>
+  <si>
+    <t>Wave_Chapter04_06</t>
+  </si>
+  <si>
+    <t>Wave_Chapter04_07</t>
+  </si>
+  <si>
+    <t>Wave_Chapter04_08</t>
+  </si>
+  <si>
+    <t>Wave_Chapter04_09</t>
+  </si>
+  <si>
+    <t>Wave_Chapter04_10</t>
+  </si>
+  <si>
+    <t>Wave_Chapter04_11</t>
+  </si>
+  <si>
+    <t>Wave_Chapter04_12</t>
+  </si>
+  <si>
+    <t>Wave_Chapter04_13</t>
+  </si>
+  <si>
+    <t>Wave_Chapter04_14</t>
+  </si>
+  <si>
+    <t>Wave_Chapter04_15</t>
+  </si>
+  <si>
+    <t>Chapter_Earth_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chapter_Earth_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chapter_Earth_4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_citizen_01,enemy_police_01</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -309,7 +463,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -325,9 +479,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -752,12 +903,12 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K1000"/>
+  <dimension ref="A1:K997"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="19.42578125" style="3" customWidth="1"/>
     <col min="3" max="3" width="19.5703125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="24.85546875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="54.28515625" style="3" customWidth="1"/>
     <col min="5" max="5" width="14.85546875" style="3" customWidth="1"/>
     <col min="6" max="6" width="13.85546875" style="3" customWidth="1"/>
     <col min="7" max="7" width="19.5703125" style="3" customWidth="1"/>
@@ -783,7 +934,7 @@
       <c r="F1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="14"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:11" ht="12.75">
       <c r="A2" s="1" t="s">
@@ -805,35 +956,35 @@
         <v>32</v>
       </c>
       <c r="G2" s="1"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-    </row>
-    <row r="3" spans="1:11" s="11" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="10" t="s">
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+    </row>
+    <row r="3" spans="1:11" s="8" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
@@ -845,16 +996,16 @@
       <c r="C4" s="4">
         <v>1</v>
       </c>
-      <c r="D4" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="15">
+      <c r="D4" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="12">
         <v>1</v>
       </c>
-      <c r="F4" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="G4" s="12"/>
+      <c r="F4" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="G4" s="9"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
@@ -866,16 +1017,16 @@
       <c r="C5" s="5">
         <v>2</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E5" s="3">
         <v>3</v>
       </c>
-      <c r="F5" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="G5" s="12"/>
+      <c r="F5" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="9"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
@@ -887,16 +1038,16 @@
       <c r="C6" s="5">
         <v>3</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E6" s="3">
         <v>5</v>
       </c>
-      <c r="F6" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="G6" s="12"/>
+      <c r="F6" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="9"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
@@ -908,16 +1059,16 @@
       <c r="C7" s="4">
         <v>4</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E7" s="3">
         <v>7</v>
       </c>
-      <c r="F7" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="G7" s="12"/>
+      <c r="F7" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="G7" s="9"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
@@ -929,16 +1080,16 @@
       <c r="C8" s="6">
         <v>5</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E8" s="3">
         <v>9</v>
       </c>
-      <c r="F8" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="G8" s="12"/>
+      <c r="F8" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="G8" s="9"/>
     </row>
     <row r="9" spans="1:11" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
@@ -950,16 +1101,16 @@
       <c r="C9" s="6">
         <v>6</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E9" s="3">
         <v>11</v>
       </c>
-      <c r="F9" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="G9" s="12"/>
+      <c r="F9" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1">
       <c r="A10" s="4" t="s">
@@ -971,16 +1122,16 @@
       <c r="C10" s="1">
         <v>7</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E10" s="3">
         <v>13</v>
       </c>
-      <c r="F10" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="G10" s="12"/>
+      <c r="F10" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1">
       <c r="A11" s="4" t="s">
@@ -992,16 +1143,16 @@
       <c r="C11" s="1">
         <v>8</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E11" s="3">
         <v>15</v>
       </c>
-      <c r="F11" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="G11" s="12"/>
+      <c r="F11" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1">
       <c r="A12" s="4" t="s">
@@ -1013,16 +1164,16 @@
       <c r="C12" s="6">
         <v>9</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E12" s="3">
         <v>17</v>
       </c>
-      <c r="F12" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="G12" s="12"/>
+      <c r="F12" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1">
       <c r="A13" s="4" t="s">
@@ -1034,13 +1185,13 @@
       <c r="C13" s="4">
         <v>10</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E13" s="3">
         <v>19</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="12">
         <v>0.5</v>
       </c>
     </row>
@@ -1054,13 +1205,13 @@
       <c r="C14" s="5">
         <v>11</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E14" s="3">
         <v>21</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="12">
         <v>0.5</v>
       </c>
     </row>
@@ -1074,13 +1225,13 @@
       <c r="C15" s="5">
         <v>12</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E15" s="3">
         <v>23</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="12">
         <v>0.5</v>
       </c>
     </row>
@@ -1094,13 +1245,13 @@
       <c r="C16" s="4">
         <v>13</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E16" s="3">
         <v>25</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="12">
         <v>0.5</v>
       </c>
     </row>
@@ -1114,13 +1265,13 @@
       <c r="C17" s="6">
         <v>14</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E17" s="3">
         <v>27</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="12">
         <v>0.5</v>
       </c>
     </row>
@@ -1134,147 +1285,917 @@
       <c r="C18" s="6">
         <v>15</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E18" s="3">
         <v>29</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="12">
         <v>0.5</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
+      <c r="A19" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="4">
+        <v>1</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="12">
+        <v>1</v>
+      </c>
+      <c r="F19" s="12">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
+      <c r="A20" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="5">
+        <v>2</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="3">
+        <v>3</v>
+      </c>
+      <c r="F20" s="12">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
+      <c r="A21" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="5">
+        <v>3</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="3">
+        <v>5</v>
+      </c>
+      <c r="F21" s="12">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
+      <c r="A22" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" s="4">
+        <v>4</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="3">
+        <v>7</v>
+      </c>
+      <c r="F22" s="12">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
+      <c r="A23" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" s="6">
+        <v>5</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="3">
+        <v>9</v>
+      </c>
+      <c r="F23" s="12">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
+      <c r="A24" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" s="6">
+        <v>6</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" s="3">
+        <v>11</v>
+      </c>
+      <c r="F24" s="12">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
+      <c r="A25" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="1">
+        <v>7</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="3">
+        <v>13</v>
+      </c>
+      <c r="F25" s="12">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
+      <c r="A26" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" s="1">
+        <v>8</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="3">
+        <v>15</v>
+      </c>
+      <c r="F26" s="12">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
+      <c r="A27" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" s="6">
+        <v>9</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="3">
+        <v>17</v>
+      </c>
+      <c r="F27" s="12">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
+      <c r="A28" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" s="4">
+        <v>10</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" s="3">
+        <v>19</v>
+      </c>
+      <c r="F28" s="12">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
+      <c r="A29" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" s="5">
+        <v>11</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" s="3">
+        <v>21</v>
+      </c>
+      <c r="F29" s="12">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
+      <c r="A30" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C30" s="5">
+        <v>12</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="3">
+        <v>23</v>
+      </c>
+      <c r="F30" s="12">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
+      <c r="A31" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" s="4">
+        <v>13</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" s="3">
+        <v>25</v>
+      </c>
+      <c r="F31" s="12">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-    </row>
-    <row r="33" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-    </row>
-    <row r="34" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-    </row>
-    <row r="35" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-    </row>
-    <row r="36" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:4" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
+      <c r="A32" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C32" s="6">
+        <v>14</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" s="3">
+        <v>27</v>
+      </c>
+      <c r="F32" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A33" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" s="6">
+        <v>15</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E33" s="3">
+        <v>29</v>
+      </c>
+      <c r="F33" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A34" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C34" s="4">
+        <v>1</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" s="12">
+        <v>1</v>
+      </c>
+      <c r="F34" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A35" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" s="5">
+        <v>2</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="3">
+        <v>3</v>
+      </c>
+      <c r="F35" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A36" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="5">
+        <v>3</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E36" s="3">
+        <v>5</v>
+      </c>
+      <c r="F36" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A37" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" s="4">
+        <v>4</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E37" s="3">
+        <v>7</v>
+      </c>
+      <c r="F37" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A38" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" s="6">
+        <v>5</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E38" s="3">
+        <v>9</v>
+      </c>
+      <c r="F38" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A39" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="6">
+        <v>6</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E39" s="3">
+        <v>11</v>
+      </c>
+      <c r="F39" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A40" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="1">
+        <v>7</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E40" s="3">
+        <v>13</v>
+      </c>
+      <c r="F40" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A41" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" s="1">
+        <v>8</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E41" s="3">
+        <v>15</v>
+      </c>
+      <c r="F41" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A42" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C42" s="6">
+        <v>9</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E42" s="3">
+        <v>17</v>
+      </c>
+      <c r="F42" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A43" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C43" s="4">
+        <v>10</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E43" s="3">
+        <v>19</v>
+      </c>
+      <c r="F43" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A44" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C44" s="5">
+        <v>11</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E44" s="3">
+        <v>21</v>
+      </c>
+      <c r="F44" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A45" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C45" s="5">
+        <v>12</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E45" s="3">
+        <v>23</v>
+      </c>
+      <c r="F45" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A46" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C46" s="4">
+        <v>13</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E46" s="3">
+        <v>25</v>
+      </c>
+      <c r="F46" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A47" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C47" s="6">
+        <v>14</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E47" s="3">
+        <v>27</v>
+      </c>
+      <c r="F47" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A48" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C48" s="6">
+        <v>15</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E48" s="3">
+        <v>29</v>
+      </c>
+      <c r="F48" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A49" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C49" s="4">
+        <v>1</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E49" s="12">
+        <v>1</v>
+      </c>
+      <c r="F49" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A50" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C50" s="5">
+        <v>2</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E50" s="3">
+        <v>3</v>
+      </c>
+      <c r="F50" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A51" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C51" s="5">
+        <v>3</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E51" s="3">
+        <v>5</v>
+      </c>
+      <c r="F51" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A52" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C52" s="4">
+        <v>4</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E52" s="3">
+        <v>7</v>
+      </c>
+      <c r="F52" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A53" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C53" s="6">
+        <v>5</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E53" s="3">
+        <v>9</v>
+      </c>
+      <c r="F53" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A54" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C54" s="6">
+        <v>6</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E54" s="3">
+        <v>11</v>
+      </c>
+      <c r="F54" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A55" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C55" s="1">
+        <v>7</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E55" s="3">
+        <v>13</v>
+      </c>
+      <c r="F55" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A56" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C56" s="1">
+        <v>8</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E56" s="3">
+        <v>15</v>
+      </c>
+      <c r="F56" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A57" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C57" s="6">
+        <v>9</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E57" s="3">
+        <v>17</v>
+      </c>
+      <c r="F57" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A58" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C58" s="4">
+        <v>10</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E58" s="3">
+        <v>19</v>
+      </c>
+      <c r="F58" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A59" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C59" s="5">
+        <v>11</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E59" s="3">
+        <v>21</v>
+      </c>
+      <c r="F59" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A60" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C60" s="5">
+        <v>12</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E60" s="3">
+        <v>23</v>
+      </c>
+      <c r="F60" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A61" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C61" s="4">
+        <v>13</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E61" s="3">
+        <v>25</v>
+      </c>
+      <c r="F61" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A62" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C62" s="6">
+        <v>14</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E62" s="3">
+        <v>27</v>
+      </c>
+      <c r="F62" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A63" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C63" s="6">
+        <v>15</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E63" s="3">
+        <v>29</v>
+      </c>
+      <c r="F63" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="15.75" customHeight="1"/>
     <row r="65" ht="15.75" customHeight="1"/>
     <row r="66" ht="15.75" customHeight="1"/>
     <row r="67" ht="15.75" customHeight="1"/>
@@ -2208,9 +3129,6 @@
     <row r="995" ht="15.75" customHeight="1"/>
     <row r="996" ht="15.75" customHeight="1"/>
     <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>

--- a/JsonConverter/ExcelFiles/WaveData.xlsx
+++ b/JsonConverter/ExcelFiles/WaveData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152788E9-93B2-447F-B92E-724BF89B1BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69238CFD-23E6-4897-9D09-BBE57CBAF9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4740" yWindow="105" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="84">
   <si>
     <t>Id</t>
   </si>
@@ -321,6 +321,13 @@
   </si>
   <si>
     <t>enemy_citizen_01,enemy_police_01</t>
+  </si>
+  <si>
+    <t>enemy_citizen_01,enemy_police_01,enemy_athlete_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_citizen_01</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -997,7 +1004,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E4" s="12">
         <v>1</v>
@@ -1306,7 +1313,7 @@
         <v>1</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="E19" s="12">
         <v>1</v>
@@ -1326,7 +1333,7 @@
         <v>2</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="E20" s="3">
         <v>3</v>
@@ -1346,7 +1353,7 @@
         <v>3</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="E21" s="3">
         <v>5</v>
@@ -1366,7 +1373,7 @@
         <v>4</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="E22" s="3">
         <v>7</v>
@@ -1386,7 +1393,7 @@
         <v>5</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="E23" s="3">
         <v>9</v>
@@ -1406,7 +1413,7 @@
         <v>6</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="E24" s="3">
         <v>11</v>
@@ -1426,7 +1433,7 @@
         <v>7</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="E25" s="3">
         <v>13</v>
@@ -1446,7 +1453,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="E26" s="3">
         <v>15</v>
@@ -1466,7 +1473,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="E27" s="3">
         <v>17</v>
@@ -1486,7 +1493,7 @@
         <v>10</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="E28" s="3">
         <v>19</v>
@@ -1506,7 +1513,7 @@
         <v>11</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="E29" s="3">
         <v>21</v>
@@ -1526,7 +1533,7 @@
         <v>12</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="E30" s="3">
         <v>23</v>
@@ -1546,7 +1553,7 @@
         <v>13</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="E31" s="3">
         <v>25</v>
@@ -1566,7 +1573,7 @@
         <v>14</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="E32" s="3">
         <v>27</v>
@@ -1586,7 +1593,7 @@
         <v>15</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="E33" s="3">
         <v>29</v>
@@ -1606,7 +1613,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E34" s="12">
         <v>1</v>
@@ -1626,7 +1633,7 @@
         <v>2</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E35" s="3">
         <v>3</v>
@@ -1646,7 +1653,7 @@
         <v>3</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E36" s="3">
         <v>5</v>
@@ -1666,7 +1673,7 @@
         <v>4</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E37" s="3">
         <v>7</v>
@@ -1686,7 +1693,7 @@
         <v>5</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E38" s="3">
         <v>9</v>
@@ -1706,7 +1713,7 @@
         <v>6</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E39" s="3">
         <v>11</v>
@@ -1726,7 +1733,7 @@
         <v>7</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E40" s="3">
         <v>13</v>
@@ -1746,7 +1753,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E41" s="3">
         <v>15</v>
@@ -1766,7 +1773,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E42" s="3">
         <v>17</v>
@@ -1786,7 +1793,7 @@
         <v>10</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E43" s="3">
         <v>19</v>
@@ -1806,7 +1813,7 @@
         <v>11</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E44" s="3">
         <v>21</v>
@@ -1826,7 +1833,7 @@
         <v>12</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E45" s="3">
         <v>23</v>
@@ -1846,7 +1853,7 @@
         <v>13</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E46" s="3">
         <v>25</v>
@@ -1866,7 +1873,7 @@
         <v>14</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E47" s="3">
         <v>27</v>
@@ -1886,7 +1893,7 @@
         <v>15</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E48" s="3">
         <v>29</v>
@@ -1906,7 +1913,7 @@
         <v>1</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E49" s="12">
         <v>1</v>
@@ -1926,7 +1933,7 @@
         <v>2</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E50" s="3">
         <v>3</v>
@@ -1946,7 +1953,7 @@
         <v>3</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E51" s="3">
         <v>5</v>
@@ -1966,7 +1973,7 @@
         <v>4</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E52" s="3">
         <v>7</v>
@@ -1986,7 +1993,7 @@
         <v>5</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E53" s="3">
         <v>9</v>
@@ -2006,7 +2013,7 @@
         <v>6</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E54" s="3">
         <v>11</v>
@@ -2026,7 +2033,7 @@
         <v>7</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E55" s="3">
         <v>13</v>
@@ -2046,7 +2053,7 @@
         <v>8</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E56" s="3">
         <v>15</v>
@@ -2066,7 +2073,7 @@
         <v>9</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E57" s="3">
         <v>17</v>
@@ -2086,7 +2093,7 @@
         <v>10</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E58" s="3">
         <v>19</v>
@@ -2106,7 +2113,7 @@
         <v>11</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E59" s="3">
         <v>21</v>
@@ -2126,7 +2133,7 @@
         <v>12</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E60" s="3">
         <v>23</v>
@@ -2146,7 +2153,7 @@
         <v>13</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E61" s="3">
         <v>25</v>
@@ -2166,7 +2173,7 @@
         <v>14</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E62" s="3">
         <v>27</v>
@@ -2186,7 +2193,7 @@
         <v>15</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E63" s="3">
         <v>29</v>

--- a/JsonConverter/ExcelFiles/WaveData.xlsx
+++ b/JsonConverter/ExcelFiles/WaveData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69238CFD-23E6-4897-9D09-BBE57CBAF9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98A23ED7-368B-4373-8944-A153F12DED6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4740" yWindow="105" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -320,14 +320,15 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>enemy_citizen_01,enemy_police_01</t>
-  </si>
-  <si>
     <t>enemy_citizen_01,enemy_police_01,enemy_athlete_01</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>enemy_citizen_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_soldiergun_01,enemy_soldierknife_01</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1004,7 +1005,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E4" s="12">
         <v>1</v>
@@ -1312,8 +1313,8 @@
       <c r="C19" s="4">
         <v>1</v>
       </c>
-      <c r="D19" s="12" t="s">
-        <v>81</v>
+      <c r="D19" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="E19" s="12">
         <v>1</v>
@@ -1332,8 +1333,8 @@
       <c r="C20" s="5">
         <v>2</v>
       </c>
-      <c r="D20" s="12" t="s">
-        <v>81</v>
+      <c r="D20" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="E20" s="3">
         <v>3</v>
@@ -1352,8 +1353,8 @@
       <c r="C21" s="5">
         <v>3</v>
       </c>
-      <c r="D21" s="12" t="s">
-        <v>81</v>
+      <c r="D21" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="E21" s="3">
         <v>5</v>
@@ -1372,8 +1373,8 @@
       <c r="C22" s="4">
         <v>4</v>
       </c>
-      <c r="D22" s="12" t="s">
-        <v>81</v>
+      <c r="D22" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="E22" s="3">
         <v>7</v>
@@ -1392,8 +1393,8 @@
       <c r="C23" s="6">
         <v>5</v>
       </c>
-      <c r="D23" s="12" t="s">
-        <v>81</v>
+      <c r="D23" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="E23" s="3">
         <v>9</v>
@@ -1412,8 +1413,8 @@
       <c r="C24" s="6">
         <v>6</v>
       </c>
-      <c r="D24" s="12" t="s">
-        <v>81</v>
+      <c r="D24" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="E24" s="3">
         <v>11</v>
@@ -1432,8 +1433,8 @@
       <c r="C25" s="1">
         <v>7</v>
       </c>
-      <c r="D25" s="12" t="s">
-        <v>81</v>
+      <c r="D25" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="E25" s="3">
         <v>13</v>
@@ -1452,8 +1453,8 @@
       <c r="C26" s="1">
         <v>8</v>
       </c>
-      <c r="D26" s="12" t="s">
-        <v>81</v>
+      <c r="D26" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="E26" s="3">
         <v>15</v>
@@ -1472,8 +1473,8 @@
       <c r="C27" s="6">
         <v>9</v>
       </c>
-      <c r="D27" s="12" t="s">
-        <v>81</v>
+      <c r="D27" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="E27" s="3">
         <v>17</v>
@@ -1492,8 +1493,8 @@
       <c r="C28" s="4">
         <v>10</v>
       </c>
-      <c r="D28" s="12" t="s">
-        <v>81</v>
+      <c r="D28" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="E28" s="3">
         <v>19</v>
@@ -1512,8 +1513,8 @@
       <c r="C29" s="5">
         <v>11</v>
       </c>
-      <c r="D29" s="12" t="s">
-        <v>81</v>
+      <c r="D29" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="E29" s="3">
         <v>21</v>
@@ -1532,8 +1533,8 @@
       <c r="C30" s="5">
         <v>12</v>
       </c>
-      <c r="D30" s="12" t="s">
-        <v>81</v>
+      <c r="D30" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="E30" s="3">
         <v>23</v>
@@ -1552,8 +1553,8 @@
       <c r="C31" s="4">
         <v>13</v>
       </c>
-      <c r="D31" s="12" t="s">
-        <v>81</v>
+      <c r="D31" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="E31" s="3">
         <v>25</v>
@@ -1572,8 +1573,8 @@
       <c r="C32" s="6">
         <v>14</v>
       </c>
-      <c r="D32" s="12" t="s">
-        <v>81</v>
+      <c r="D32" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="E32" s="3">
         <v>27</v>
@@ -1592,8 +1593,8 @@
       <c r="C33" s="6">
         <v>15</v>
       </c>
-      <c r="D33" s="12" t="s">
-        <v>81</v>
+      <c r="D33" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="E33" s="3">
         <v>29</v>
@@ -1613,7 +1614,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E34" s="12">
         <v>1</v>
@@ -1633,7 +1634,7 @@
         <v>2</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E35" s="3">
         <v>3</v>
@@ -1653,7 +1654,7 @@
         <v>3</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E36" s="3">
         <v>5</v>
@@ -1673,7 +1674,7 @@
         <v>4</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E37" s="3">
         <v>7</v>
@@ -1693,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E38" s="3">
         <v>9</v>
@@ -1713,7 +1714,7 @@
         <v>6</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E39" s="3">
         <v>11</v>
@@ -1733,7 +1734,7 @@
         <v>7</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E40" s="3">
         <v>13</v>
@@ -1753,7 +1754,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E41" s="3">
         <v>15</v>
@@ -1773,7 +1774,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E42" s="3">
         <v>17</v>
@@ -1793,7 +1794,7 @@
         <v>10</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E43" s="3">
         <v>19</v>
@@ -1813,7 +1814,7 @@
         <v>11</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E44" s="3">
         <v>21</v>
@@ -1833,7 +1834,7 @@
         <v>12</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E45" s="3">
         <v>23</v>
@@ -1853,7 +1854,7 @@
         <v>13</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E46" s="3">
         <v>25</v>
@@ -1873,7 +1874,7 @@
         <v>14</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E47" s="3">
         <v>27</v>
@@ -1893,7 +1894,7 @@
         <v>15</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E48" s="3">
         <v>29</v>
@@ -1913,7 +1914,7 @@
         <v>1</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E49" s="12">
         <v>1</v>
@@ -1933,7 +1934,7 @@
         <v>2</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E50" s="3">
         <v>3</v>
@@ -1953,7 +1954,7 @@
         <v>3</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E51" s="3">
         <v>5</v>
@@ -1973,7 +1974,7 @@
         <v>4</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E52" s="3">
         <v>7</v>
@@ -1993,7 +1994,7 @@
         <v>5</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E53" s="3">
         <v>9</v>
@@ -2013,7 +2014,7 @@
         <v>6</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E54" s="3">
         <v>11</v>
@@ -2033,7 +2034,7 @@
         <v>7</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E55" s="3">
         <v>13</v>
@@ -2053,7 +2054,7 @@
         <v>8</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E56" s="3">
         <v>15</v>
@@ -2073,7 +2074,7 @@
         <v>9</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E57" s="3">
         <v>17</v>
@@ -2093,7 +2094,7 @@
         <v>10</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E58" s="3">
         <v>19</v>
@@ -2113,7 +2114,7 @@
         <v>11</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E59" s="3">
         <v>21</v>
@@ -2133,7 +2134,7 @@
         <v>12</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E60" s="3">
         <v>23</v>
@@ -2153,7 +2154,7 @@
         <v>13</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E61" s="3">
         <v>25</v>
@@ -2173,7 +2174,7 @@
         <v>14</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E62" s="3">
         <v>27</v>
@@ -2193,7 +2194,7 @@
         <v>15</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E63" s="3">
         <v>29</v>

--- a/JsonConverter/ExcelFiles/WaveData.xlsx
+++ b/JsonConverter/ExcelFiles/WaveData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98A23ED7-368B-4373-8944-A153F12DED6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F23F1DDD-DBDC-4D67-8A59-B4AFC46A3C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4740" yWindow="105" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1305" yWindow="465" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
   <si>
     <t>Id</t>
   </si>
@@ -329,6 +329,38 @@
   </si>
   <si>
     <t>enemy_soldiergun_01,enemy_soldierknife_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_tank_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_tank_01,enemy_firetank_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_tank_01,enemy_firetank_01,enemy_drill_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_firetank_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_drill_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_citizen_01,enemy_athlete_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_soldierknife_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_soldiergun_01</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1008,7 +1040,7 @@
         <v>82</v>
       </c>
       <c r="E4" s="12">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F4" s="12">
         <v>0.5</v>
@@ -1029,7 +1061,7 @@
         <v>30</v>
       </c>
       <c r="E5" s="3">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F5" s="12">
         <v>0.5</v>
@@ -1050,7 +1082,7 @@
         <v>30</v>
       </c>
       <c r="E6" s="3">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F6" s="12">
         <v>0.5</v>
@@ -1071,7 +1103,7 @@
         <v>30</v>
       </c>
       <c r="E7" s="3">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F7" s="12">
         <v>0.5</v>
@@ -1092,7 +1124,7 @@
         <v>30</v>
       </c>
       <c r="E8" s="3">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F8" s="12">
         <v>0.5</v>
@@ -1110,10 +1142,10 @@
         <v>6</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="E9" s="3">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F9" s="12">
         <v>0.5</v>
@@ -1131,10 +1163,10 @@
         <v>7</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="E10" s="3">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F10" s="12">
         <v>0.5</v>
@@ -1152,10 +1184,10 @@
         <v>8</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="E11" s="3">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F11" s="12">
         <v>0.5</v>
@@ -1173,10 +1205,10 @@
         <v>9</v>
       </c>
       <c r="D12" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" s="3">
         <v>30</v>
-      </c>
-      <c r="E12" s="3">
-        <v>17</v>
       </c>
       <c r="F12" s="12">
         <v>0.5</v>
@@ -1194,10 +1226,10 @@
         <v>10</v>
       </c>
       <c r="D13" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="3">
         <v>30</v>
-      </c>
-      <c r="E13" s="3">
-        <v>19</v>
       </c>
       <c r="F13" s="12">
         <v>0.5</v>
@@ -1214,10 +1246,10 @@
         <v>11</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="E14" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F14" s="12">
         <v>0.5</v>
@@ -1234,7 +1266,7 @@
         <v>12</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="E15" s="3">
         <v>23</v>
@@ -1254,7 +1286,7 @@
         <v>13</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="E16" s="3">
         <v>25</v>
@@ -1274,10 +1306,10 @@
         <v>14</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="E17" s="3">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F17" s="12">
         <v>0.5</v>
@@ -1294,10 +1326,10 @@
         <v>15</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="E18" s="3">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="F18" s="12">
         <v>0.5</v>
@@ -1314,10 +1346,10 @@
         <v>1</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E19" s="12">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F19" s="12">
         <v>0.5</v>
@@ -1334,10 +1366,10 @@
         <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E20" s="3">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F20" s="12">
         <v>0.5</v>
@@ -1354,10 +1386,10 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="E21" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F21" s="12">
         <v>0.5</v>
@@ -1374,10 +1406,10 @@
         <v>4</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="E22" s="3">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F22" s="12">
         <v>0.5</v>
@@ -1397,7 +1429,7 @@
         <v>83</v>
       </c>
       <c r="E23" s="3">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F23" s="12">
         <v>0.5</v>
@@ -1414,10 +1446,10 @@
         <v>6</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E24" s="3">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F24" s="12">
         <v>0.5</v>
@@ -1434,10 +1466,10 @@
         <v>7</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E25" s="3">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F25" s="12">
         <v>0.5</v>
@@ -1454,10 +1486,10 @@
         <v>8</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="E26" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F26" s="12">
         <v>0.5</v>
@@ -1474,10 +1506,10 @@
         <v>9</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="E27" s="3">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F27" s="12">
         <v>0.5</v>
@@ -1497,7 +1529,7 @@
         <v>83</v>
       </c>
       <c r="E28" s="3">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F28" s="12">
         <v>0.5</v>
@@ -1514,10 +1546,10 @@
         <v>11</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E29" s="3">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F29" s="12">
         <v>0.5</v>
@@ -1534,10 +1566,10 @@
         <v>12</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="E30" s="3">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F30" s="12">
         <v>0.5</v>
@@ -1557,7 +1589,7 @@
         <v>83</v>
       </c>
       <c r="E31" s="3">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F31" s="12">
         <v>0.5</v>
@@ -1577,7 +1609,7 @@
         <v>83</v>
       </c>
       <c r="E32" s="3">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F32" s="12">
         <v>0.5</v>
@@ -1597,7 +1629,7 @@
         <v>83</v>
       </c>
       <c r="E33" s="3">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="F33" s="12">
         <v>0.5</v>
@@ -1613,14 +1645,14 @@
       <c r="C34" s="4">
         <v>1</v>
       </c>
-      <c r="D34" s="12" t="s">
-        <v>81</v>
+      <c r="D34" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="E34" s="12">
+        <v>5</v>
+      </c>
+      <c r="F34" s="12">
         <v>1</v>
-      </c>
-      <c r="F34" s="12">
-        <v>0.5</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" customHeight="1">
@@ -1633,14 +1665,14 @@
       <c r="C35" s="5">
         <v>2</v>
       </c>
-      <c r="D35" s="12" t="s">
-        <v>81</v>
+      <c r="D35" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="E35" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F35" s="12">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1">
@@ -1653,14 +1685,14 @@
       <c r="C36" s="5">
         <v>3</v>
       </c>
-      <c r="D36" s="12" t="s">
-        <v>81</v>
+      <c r="D36" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="E36" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F36" s="12">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" customHeight="1">
@@ -1673,14 +1705,14 @@
       <c r="C37" s="4">
         <v>4</v>
       </c>
-      <c r="D37" s="12" t="s">
-        <v>81</v>
+      <c r="D37" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="E37" s="3">
         <v>7</v>
       </c>
       <c r="F37" s="12">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" customHeight="1">
@@ -1693,14 +1725,14 @@
       <c r="C38" s="6">
         <v>5</v>
       </c>
-      <c r="D38" s="12" t="s">
-        <v>81</v>
+      <c r="D38" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="E38" s="3">
         <v>9</v>
       </c>
       <c r="F38" s="12">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" customHeight="1">
@@ -1713,14 +1745,14 @@
       <c r="C39" s="6">
         <v>6</v>
       </c>
-      <c r="D39" s="12" t="s">
-        <v>81</v>
+      <c r="D39" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="E39" s="3">
         <v>11</v>
       </c>
       <c r="F39" s="12">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" customHeight="1">
@@ -1733,14 +1765,14 @@
       <c r="C40" s="1">
         <v>7</v>
       </c>
-      <c r="D40" s="12" t="s">
-        <v>81</v>
+      <c r="D40" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="E40" s="3">
         <v>13</v>
       </c>
       <c r="F40" s="12">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" customHeight="1">
@@ -1753,14 +1785,14 @@
       <c r="C41" s="1">
         <v>8</v>
       </c>
-      <c r="D41" s="12" t="s">
-        <v>81</v>
+      <c r="D41" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="E41" s="3">
         <v>15</v>
       </c>
       <c r="F41" s="12">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" customHeight="1">
@@ -1773,14 +1805,14 @@
       <c r="C42" s="6">
         <v>9</v>
       </c>
-      <c r="D42" s="12" t="s">
-        <v>81</v>
+      <c r="D42" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="E42" s="3">
         <v>17</v>
       </c>
       <c r="F42" s="12">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.75" customHeight="1">
@@ -1793,14 +1825,14 @@
       <c r="C43" s="4">
         <v>10</v>
       </c>
-      <c r="D43" s="12" t="s">
-        <v>81</v>
+      <c r="D43" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="E43" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F43" s="12">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" customHeight="1">
@@ -1813,14 +1845,14 @@
       <c r="C44" s="5">
         <v>11</v>
       </c>
-      <c r="D44" s="12" t="s">
-        <v>81</v>
+      <c r="D44" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="E44" s="3">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F44" s="12">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" customHeight="1">
@@ -1833,14 +1865,14 @@
       <c r="C45" s="5">
         <v>12</v>
       </c>
-      <c r="D45" s="12" t="s">
-        <v>81</v>
+      <c r="D45" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="E45" s="3">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F45" s="12">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" customHeight="1">
@@ -1853,14 +1885,14 @@
       <c r="C46" s="4">
         <v>13</v>
       </c>
-      <c r="D46" s="12" t="s">
-        <v>81</v>
+      <c r="D46" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="E46" s="3">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F46" s="12">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" customHeight="1">
@@ -1873,14 +1905,14 @@
       <c r="C47" s="6">
         <v>14</v>
       </c>
-      <c r="D47" s="12" t="s">
-        <v>81</v>
+      <c r="D47" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="E47" s="3">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="F47" s="12">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" customHeight="1">
@@ -1893,14 +1925,14 @@
       <c r="C48" s="6">
         <v>15</v>
       </c>
-      <c r="D48" s="12" t="s">
-        <v>81</v>
+      <c r="D48" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="E48" s="3">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="F48" s="12">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/WaveData.xlsx
+++ b/JsonConverter/ExcelFiles/WaveData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F23F1DDD-DBDC-4D67-8A59-B4AFC46A3C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD289214-81BC-45D9-840C-FF9854507642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1305" yWindow="465" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4965" yWindow="300" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="95">
   <si>
     <t>Id</t>
   </si>
@@ -361,6 +361,17 @@
   </si>
   <si>
     <t>enemy_soldiergun_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave_Chapter06_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave_Chapter06_02</t>
+  </si>
+  <si>
+    <t>Chapter_Earth_6</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -2235,23 +2246,100 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="64" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A64" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C64" s="3">
+        <v>1</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E64" s="3">
+        <v>1</v>
+      </c>
+      <c r="F64" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A65" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C65" s="3">
+        <v>2</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E65" s="3">
+        <v>1</v>
+      </c>
+      <c r="F65" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A66" s="4"/>
+      <c r="B66" s="4"/>
+    </row>
+    <row r="67" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A67" s="4"/>
+      <c r="B67" s="4"/>
+    </row>
+    <row r="68" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A68" s="4"/>
+      <c r="B68" s="4"/>
+    </row>
+    <row r="69" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A69" s="4"/>
+      <c r="B69" s="4"/>
+    </row>
+    <row r="70" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A70" s="4"/>
+      <c r="B70" s="4"/>
+    </row>
+    <row r="71" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A71" s="4"/>
+      <c r="B71" s="4"/>
+    </row>
+    <row r="72" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A72" s="4"/>
+      <c r="B72" s="4"/>
+    </row>
+    <row r="73" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A73" s="4"/>
+      <c r="B73" s="4"/>
+    </row>
+    <row r="74" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A74" s="4"/>
+      <c r="B74" s="4"/>
+    </row>
+    <row r="75" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A75" s="4"/>
+      <c r="B75" s="4"/>
+    </row>
+    <row r="76" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A76" s="4"/>
+      <c r="B76" s="4"/>
+    </row>
+    <row r="77" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A77" s="4"/>
+      <c r="B77" s="4"/>
+    </row>
+    <row r="78" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A78" s="4"/>
+      <c r="B78" s="4"/>
+    </row>
+    <row r="79" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="80" spans="1:6" ht="15.75" customHeight="1"/>
     <row r="81" ht="15.75" customHeight="1"/>
     <row r="82" ht="15.75" customHeight="1"/>
     <row r="83" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/WaveData.xlsx
+++ b/JsonConverter/ExcelFiles/WaveData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD289214-81BC-45D9-840C-FF9854507642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED8DC20-DF5C-4B9A-A680-8946C40F55C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4965" yWindow="300" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="720" windowWidth="28770" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="126">
   <si>
     <t>Id</t>
   </si>
@@ -374,12 +374,109 @@
     <t>Chapter_Earth_6</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>Wave_Chapter06_03</t>
+  </si>
+  <si>
+    <t>Wave_Chapter06_04</t>
+  </si>
+  <si>
+    <t>Wave_Chapter06_05</t>
+  </si>
+  <si>
+    <t>Wave_Chapter06_06</t>
+  </si>
+  <si>
+    <t>Wave_Chapter06_07</t>
+  </si>
+  <si>
+    <t>Wave_Chapter06_08</t>
+  </si>
+  <si>
+    <t>Wave_Chapter06_09</t>
+  </si>
+  <si>
+    <t>Wave_Chapter06_10</t>
+  </si>
+  <si>
+    <t>Wave_Chapter06_11</t>
+  </si>
+  <si>
+    <t>Wave_Chapter06_12</t>
+  </si>
+  <si>
+    <t>Wave_Chapter06_13</t>
+  </si>
+  <si>
+    <t>Wave_Chapter06_14</t>
+  </si>
+  <si>
+    <t>Wave_Chapter06_15</t>
+  </si>
+  <si>
+    <t>Wave_Chapter05_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave_Chapter05_02</t>
+  </si>
+  <si>
+    <t>Wave_Chapter05_03</t>
+  </si>
+  <si>
+    <t>Wave_Chapter05_04</t>
+  </si>
+  <si>
+    <t>Wave_Chapter05_05</t>
+  </si>
+  <si>
+    <t>Wave_Chapter05_06</t>
+  </si>
+  <si>
+    <t>Wave_Chapter05_07</t>
+  </si>
+  <si>
+    <t>Wave_Chapter05_08</t>
+  </si>
+  <si>
+    <t>Wave_Chapter05_09</t>
+  </si>
+  <si>
+    <t>Wave_Chapter05_10</t>
+  </si>
+  <si>
+    <t>Wave_Chapter05_11</t>
+  </si>
+  <si>
+    <t>Wave_Chapter05_12</t>
+  </si>
+  <si>
+    <t>Wave_Chapter05_13</t>
+  </si>
+  <si>
+    <t>Wave_Chapter05_14</t>
+  </si>
+  <si>
+    <t>Wave_Chapter05_15</t>
+  </si>
+  <si>
+    <t>Chapter_Earth_5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave_Chapter07_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chapter_Earth_7</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -417,13 +514,6 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
   </fonts>
   <fills count="8">
@@ -470,7 +560,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -493,28 +583,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -534,11 +609,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -954,7 +1025,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K997"/>
+  <dimension ref="A1:J997"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="19.42578125" style="3" customWidth="1"/>
@@ -962,13 +1033,12 @@
     <col min="4" max="4" width="54.28515625" style="3" customWidth="1"/>
     <col min="5" max="5" width="14.85546875" style="3" customWidth="1"/>
     <col min="6" max="6" width="13.85546875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" style="3" customWidth="1"/>
-    <col min="8" max="10" width="12.5703125" style="3"/>
-    <col min="11" max="11" width="15.85546875" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="12.5703125" style="3"/>
+    <col min="7" max="9" width="12.5703125" style="3"/>
+    <col min="10" max="10" width="15.85546875" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="12.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" customHeight="1">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -985,9 +1055,8 @@
       <c r="F1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="11"/>
-    </row>
-    <row r="2" spans="1:11" ht="12.75">
+    </row>
+    <row r="2" spans="1:10" ht="12.75">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1006,13 +1075,12 @@
       <c r="F2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-    </row>
-    <row r="3" spans="1:11" s="8" customFormat="1" ht="15.75" customHeight="1">
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+    </row>
+    <row r="3" spans="1:10" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
@@ -1025,19 +1093,18 @@
       <c r="D3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-    </row>
-    <row r="4" spans="1:11" ht="15.75" customHeight="1">
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
@@ -1047,18 +1114,17 @@
       <c r="C4" s="4">
         <v>1</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="10">
         <v>15</v>
       </c>
-      <c r="F4" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="G4" s="9"/>
-    </row>
-    <row r="5" spans="1:11" ht="15.75" customHeight="1">
+      <c r="F4" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
@@ -1068,18 +1134,17 @@
       <c r="C5" s="5">
         <v>2</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="10" t="s">
         <v>30</v>
       </c>
       <c r="E5" s="3">
         <v>15</v>
       </c>
-      <c r="F5" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="G5" s="9"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.75" customHeight="1">
+      <c r="F5" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
@@ -1089,18 +1154,17 @@
       <c r="C6" s="5">
         <v>3</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="10" t="s">
         <v>30</v>
       </c>
       <c r="E6" s="3">
         <v>20</v>
       </c>
-      <c r="F6" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="G6" s="9"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" customHeight="1">
+      <c r="F6" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
@@ -1110,18 +1174,17 @@
       <c r="C7" s="4">
         <v>4</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="10" t="s">
         <v>30</v>
       </c>
       <c r="E7" s="3">
         <v>20</v>
       </c>
-      <c r="F7" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="G7" s="9"/>
-    </row>
-    <row r="8" spans="1:11" ht="15.75" customHeight="1">
+      <c r="F7" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>16</v>
       </c>
@@ -1131,18 +1194,17 @@
       <c r="C8" s="6">
         <v>5</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="10" t="s">
         <v>30</v>
       </c>
       <c r="E8" s="3">
         <v>30</v>
       </c>
-      <c r="F8" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="G8" s="9"/>
-    </row>
-    <row r="9" spans="1:11" ht="15.75" customHeight="1">
+      <c r="F8" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>17</v>
       </c>
@@ -1152,18 +1214,17 @@
       <c r="C9" s="6">
         <v>6</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="10" t="s">
         <v>89</v>
       </c>
       <c r="E9" s="3">
         <v>20</v>
       </c>
-      <c r="F9" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="G9" s="9"/>
-    </row>
-    <row r="10" spans="1:11" ht="15.75" customHeight="1">
+      <c r="F9" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>18</v>
       </c>
@@ -1173,18 +1234,17 @@
       <c r="C10" s="1">
         <v>7</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="10" t="s">
         <v>89</v>
       </c>
       <c r="E10" s="3">
         <v>25</v>
       </c>
-      <c r="F10" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="G10" s="9"/>
-    </row>
-    <row r="11" spans="1:11" ht="15.75" customHeight="1">
+      <c r="F10" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>19</v>
       </c>
@@ -1194,18 +1254,17 @@
       <c r="C11" s="1">
         <v>8</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="10" t="s">
         <v>89</v>
       </c>
       <c r="E11" s="3">
         <v>25</v>
       </c>
-      <c r="F11" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="G11" s="9"/>
-    </row>
-    <row r="12" spans="1:11" ht="15.75" customHeight="1">
+      <c r="F11" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>20</v>
       </c>
@@ -1215,18 +1274,17 @@
       <c r="C12" s="6">
         <v>9</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="10" t="s">
         <v>89</v>
       </c>
       <c r="E12" s="3">
         <v>30</v>
       </c>
-      <c r="F12" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="G12" s="9"/>
-    </row>
-    <row r="13" spans="1:11" ht="15.75" customHeight="1">
+      <c r="F12" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>21</v>
       </c>
@@ -1236,17 +1294,17 @@
       <c r="C13" s="4">
         <v>10</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="10" t="s">
         <v>89</v>
       </c>
       <c r="E13" s="3">
         <v>30</v>
       </c>
-      <c r="F13" s="12">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="15.75" customHeight="1">
+      <c r="F13" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>22</v>
       </c>
@@ -1256,17 +1314,17 @@
       <c r="C14" s="5">
         <v>11</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="10" t="s">
         <v>81</v>
       </c>
       <c r="E14" s="3">
         <v>20</v>
       </c>
-      <c r="F14" s="12">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="15.75" customHeight="1">
+      <c r="F14" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
@@ -1276,17 +1334,17 @@
       <c r="C15" s="5">
         <v>12</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="10" t="s">
         <v>81</v>
       </c>
       <c r="E15" s="3">
         <v>23</v>
       </c>
-      <c r="F15" s="12">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="15.75" customHeight="1">
+      <c r="F15" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>24</v>
       </c>
@@ -1296,13 +1354,13 @@
       <c r="C16" s="4">
         <v>13</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="10" t="s">
         <v>81</v>
       </c>
       <c r="E16" s="3">
         <v>25</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -1316,13 +1374,13 @@
       <c r="C17" s="6">
         <v>14</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="10" t="s">
         <v>81</v>
       </c>
       <c r="E17" s="3">
         <v>35</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -1336,13 +1394,13 @@
       <c r="C18" s="6">
         <v>15</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="10" t="s">
         <v>81</v>
       </c>
       <c r="E18" s="3">
         <v>40</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -1359,10 +1417,10 @@
       <c r="D19" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="10">
         <v>10</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -1382,7 +1440,7 @@
       <c r="E20" s="3">
         <v>15</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -1402,7 +1460,7 @@
       <c r="E21" s="3">
         <v>10</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -1422,7 +1480,7 @@
       <c r="E22" s="3">
         <v>15</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -1442,7 +1500,7 @@
       <c r="E23" s="3">
         <v>20</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -1462,7 +1520,7 @@
       <c r="E24" s="3">
         <v>20</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -1482,7 +1540,7 @@
       <c r="E25" s="3">
         <v>25</v>
       </c>
-      <c r="F25" s="12">
+      <c r="F25" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -1502,7 +1560,7 @@
       <c r="E26" s="3">
         <v>20</v>
       </c>
-      <c r="F26" s="12">
+      <c r="F26" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -1522,7 +1580,7 @@
       <c r="E27" s="3">
         <v>25</v>
       </c>
-      <c r="F27" s="12">
+      <c r="F27" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -1542,7 +1600,7 @@
       <c r="E28" s="3">
         <v>30</v>
       </c>
-      <c r="F28" s="12">
+      <c r="F28" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -1562,7 +1620,7 @@
       <c r="E29" s="3">
         <v>30</v>
       </c>
-      <c r="F29" s="12">
+      <c r="F29" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -1582,7 +1640,7 @@
       <c r="E30" s="3">
         <v>30</v>
       </c>
-      <c r="F30" s="12">
+      <c r="F30" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -1602,7 +1660,7 @@
       <c r="E31" s="3">
         <v>35</v>
       </c>
-      <c r="F31" s="12">
+      <c r="F31" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -1622,7 +1680,7 @@
       <c r="E32" s="3">
         <v>40</v>
       </c>
-      <c r="F32" s="12">
+      <c r="F32" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -1642,7 +1700,7 @@
       <c r="E33" s="3">
         <v>50</v>
       </c>
-      <c r="F33" s="12">
+      <c r="F33" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -1659,10 +1717,10 @@
       <c r="D34" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="E34" s="12">
+      <c r="E34" s="10">
         <v>5</v>
       </c>
-      <c r="F34" s="12">
+      <c r="F34" s="10">
         <v>1</v>
       </c>
     </row>
@@ -1682,7 +1740,7 @@
       <c r="E35" s="3">
         <v>10</v>
       </c>
-      <c r="F35" s="12">
+      <c r="F35" s="10">
         <v>1</v>
       </c>
     </row>
@@ -1702,7 +1760,7 @@
       <c r="E36" s="3">
         <v>3</v>
       </c>
-      <c r="F36" s="12">
+      <c r="F36" s="10">
         <v>1</v>
       </c>
     </row>
@@ -1722,7 +1780,7 @@
       <c r="E37" s="3">
         <v>7</v>
       </c>
-      <c r="F37" s="12">
+      <c r="F37" s="10">
         <v>1.5</v>
       </c>
     </row>
@@ -1742,7 +1800,7 @@
       <c r="E38" s="3">
         <v>9</v>
       </c>
-      <c r="F38" s="12">
+      <c r="F38" s="10">
         <v>1.5</v>
       </c>
     </row>
@@ -1762,7 +1820,7 @@
       <c r="E39" s="3">
         <v>11</v>
       </c>
-      <c r="F39" s="12">
+      <c r="F39" s="10">
         <v>1.5</v>
       </c>
     </row>
@@ -1782,7 +1840,7 @@
       <c r="E40" s="3">
         <v>13</v>
       </c>
-      <c r="F40" s="12">
+      <c r="F40" s="10">
         <v>1.5</v>
       </c>
     </row>
@@ -1802,7 +1860,7 @@
       <c r="E41" s="3">
         <v>15</v>
       </c>
-      <c r="F41" s="12">
+      <c r="F41" s="10">
         <v>1.5</v>
       </c>
     </row>
@@ -1822,7 +1880,7 @@
       <c r="E42" s="3">
         <v>17</v>
       </c>
-      <c r="F42" s="12">
+      <c r="F42" s="10">
         <v>1.5</v>
       </c>
     </row>
@@ -1842,7 +1900,7 @@
       <c r="E43" s="3">
         <v>20</v>
       </c>
-      <c r="F43" s="12">
+      <c r="F43" s="10">
         <v>2</v>
       </c>
     </row>
@@ -1862,7 +1920,7 @@
       <c r="E44" s="3">
         <v>30</v>
       </c>
-      <c r="F44" s="12">
+      <c r="F44" s="10">
         <v>2</v>
       </c>
     </row>
@@ -1882,7 +1940,7 @@
       <c r="E45" s="3">
         <v>35</v>
       </c>
-      <c r="F45" s="12">
+      <c r="F45" s="10">
         <v>2</v>
       </c>
     </row>
@@ -1902,7 +1960,7 @@
       <c r="E46" s="3">
         <v>40</v>
       </c>
-      <c r="F46" s="12">
+      <c r="F46" s="10">
         <v>2</v>
       </c>
     </row>
@@ -1922,7 +1980,7 @@
       <c r="E47" s="3">
         <v>45</v>
       </c>
-      <c r="F47" s="12">
+      <c r="F47" s="10">
         <v>2</v>
       </c>
     </row>
@@ -1942,7 +2000,7 @@
       <c r="E48" s="3">
         <v>50</v>
       </c>
-      <c r="F48" s="12">
+      <c r="F48" s="10">
         <v>2</v>
       </c>
     </row>
@@ -1956,13 +2014,13 @@
       <c r="C49" s="4">
         <v>1</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="D49" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="E49" s="12">
+      <c r="E49" s="10">
         <v>1</v>
       </c>
-      <c r="F49" s="12">
+      <c r="F49" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -1976,13 +2034,13 @@
       <c r="C50" s="5">
         <v>2</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="10" t="s">
         <v>81</v>
       </c>
       <c r="E50" s="3">
         <v>3</v>
       </c>
-      <c r="F50" s="12">
+      <c r="F50" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -1996,13 +2054,13 @@
       <c r="C51" s="5">
         <v>3</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="10" t="s">
         <v>81</v>
       </c>
       <c r="E51" s="3">
         <v>5</v>
       </c>
-      <c r="F51" s="12">
+      <c r="F51" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -2016,13 +2074,13 @@
       <c r="C52" s="4">
         <v>4</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="D52" s="10" t="s">
         <v>81</v>
       </c>
       <c r="E52" s="3">
         <v>7</v>
       </c>
-      <c r="F52" s="12">
+      <c r="F52" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -2036,13 +2094,13 @@
       <c r="C53" s="6">
         <v>5</v>
       </c>
-      <c r="D53" s="12" t="s">
+      <c r="D53" s="10" t="s">
         <v>81</v>
       </c>
       <c r="E53" s="3">
         <v>9</v>
       </c>
-      <c r="F53" s="12">
+      <c r="F53" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -2056,13 +2114,13 @@
       <c r="C54" s="6">
         <v>6</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="D54" s="10" t="s">
         <v>81</v>
       </c>
       <c r="E54" s="3">
         <v>11</v>
       </c>
-      <c r="F54" s="12">
+      <c r="F54" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -2076,13 +2134,13 @@
       <c r="C55" s="1">
         <v>7</v>
       </c>
-      <c r="D55" s="12" t="s">
+      <c r="D55" s="10" t="s">
         <v>81</v>
       </c>
       <c r="E55" s="3">
         <v>13</v>
       </c>
-      <c r="F55" s="12">
+      <c r="F55" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -2096,13 +2154,13 @@
       <c r="C56" s="1">
         <v>8</v>
       </c>
-      <c r="D56" s="12" t="s">
+      <c r="D56" s="10" t="s">
         <v>81</v>
       </c>
       <c r="E56" s="3">
         <v>15</v>
       </c>
-      <c r="F56" s="12">
+      <c r="F56" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -2116,13 +2174,13 @@
       <c r="C57" s="6">
         <v>9</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="D57" s="10" t="s">
         <v>81</v>
       </c>
       <c r="E57" s="3">
         <v>17</v>
       </c>
-      <c r="F57" s="12">
+      <c r="F57" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -2136,13 +2194,13 @@
       <c r="C58" s="4">
         <v>10</v>
       </c>
-      <c r="D58" s="12" t="s">
+      <c r="D58" s="10" t="s">
         <v>81</v>
       </c>
       <c r="E58" s="3">
         <v>19</v>
       </c>
-      <c r="F58" s="12">
+      <c r="F58" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -2156,13 +2214,13 @@
       <c r="C59" s="5">
         <v>11</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="D59" s="10" t="s">
         <v>81</v>
       </c>
       <c r="E59" s="3">
         <v>21</v>
       </c>
-      <c r="F59" s="12">
+      <c r="F59" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -2176,13 +2234,13 @@
       <c r="C60" s="5">
         <v>12</v>
       </c>
-      <c r="D60" s="12" t="s">
+      <c r="D60" s="10" t="s">
         <v>81</v>
       </c>
       <c r="E60" s="3">
         <v>23</v>
       </c>
-      <c r="F60" s="12">
+      <c r="F60" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -2196,13 +2254,13 @@
       <c r="C61" s="4">
         <v>13</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="D61" s="10" t="s">
         <v>81</v>
       </c>
       <c r="E61" s="3">
         <v>25</v>
       </c>
-      <c r="F61" s="12">
+      <c r="F61" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -2216,13 +2274,13 @@
       <c r="C62" s="6">
         <v>14</v>
       </c>
-      <c r="D62" s="12" t="s">
+      <c r="D62" s="10" t="s">
         <v>81</v>
       </c>
       <c r="E62" s="3">
         <v>27</v>
       </c>
-      <c r="F62" s="12">
+      <c r="F62" s="10">
         <v>0.5</v>
       </c>
     </row>
@@ -2236,27 +2294,27 @@
       <c r="C63" s="6">
         <v>15</v>
       </c>
-      <c r="D63" s="12" t="s">
+      <c r="D63" s="10" t="s">
         <v>81</v>
       </c>
       <c r="E63" s="3">
         <v>29</v>
       </c>
-      <c r="F63" s="12">
+      <c r="F63" s="10">
         <v>0.5</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15.75" customHeight="1">
       <c r="A64" s="4" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C64" s="3">
+        <v>123</v>
+      </c>
+      <c r="C64" s="4">
         <v>1</v>
       </c>
-      <c r="D64" s="12" t="s">
+      <c r="D64" s="10" t="s">
         <v>82</v>
       </c>
       <c r="E64" s="3">
@@ -2268,15 +2326,15 @@
     </row>
     <row r="65" spans="1:6" ht="15.75" customHeight="1">
       <c r="A65" s="4" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C65" s="3">
+        <v>123</v>
+      </c>
+      <c r="C65" s="5">
         <v>2</v>
       </c>
-      <c r="D65" s="12" t="s">
+      <c r="D65" s="10" t="s">
         <v>82</v>
       </c>
       <c r="E65" s="3">
@@ -2287,91 +2345,409 @@
       </c>
     </row>
     <row r="66" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A66" s="4"/>
-      <c r="B66" s="4"/>
+      <c r="A66" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C66" s="5">
+        <v>3</v>
+      </c>
     </row>
     <row r="67" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A67" s="4"/>
-      <c r="B67" s="4"/>
+      <c r="A67" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C67" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="68" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A68" s="4"/>
-      <c r="B68" s="4"/>
+      <c r="A68" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C68" s="6">
+        <v>5</v>
+      </c>
     </row>
     <row r="69" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A69" s="4"/>
-      <c r="B69" s="4"/>
+      <c r="A69" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C69" s="6">
+        <v>6</v>
+      </c>
     </row>
     <row r="70" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A70" s="4"/>
-      <c r="B70" s="4"/>
+      <c r="A70" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C70" s="1">
+        <v>7</v>
+      </c>
     </row>
     <row r="71" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A71" s="4"/>
-      <c r="B71" s="4"/>
+      <c r="A71" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C71" s="1">
+        <v>8</v>
+      </c>
     </row>
     <row r="72" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A72" s="4"/>
-      <c r="B72" s="4"/>
+      <c r="A72" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C72" s="6">
+        <v>9</v>
+      </c>
     </row>
     <row r="73" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A73" s="4"/>
-      <c r="B73" s="4"/>
+      <c r="A73" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C73" s="4">
+        <v>10</v>
+      </c>
     </row>
     <row r="74" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A74" s="4"/>
-      <c r="B74" s="4"/>
+      <c r="A74" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C74" s="5">
+        <v>11</v>
+      </c>
     </row>
     <row r="75" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A75" s="4"/>
-      <c r="B75" s="4"/>
+      <c r="A75" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C75" s="5">
+        <v>12</v>
+      </c>
     </row>
     <row r="76" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A76" s="4"/>
-      <c r="B76" s="4"/>
+      <c r="A76" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C76" s="4">
+        <v>13</v>
+      </c>
     </row>
     <row r="77" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
+      <c r="A77" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C77" s="6">
+        <v>14</v>
+      </c>
     </row>
     <row r="78" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A78" s="4"/>
-      <c r="B78" s="4"/>
-    </row>
-    <row r="79" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="80" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
+      <c r="A78" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C78" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A79" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C79" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A80" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C80" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A81" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C81" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A82" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C82" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A83" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C83" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A84" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C84" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A85" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C85" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A86" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C86" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A87" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C87" s="6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A88" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C88" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A89" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C89" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A90" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C90" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A91" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C91" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A92" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C92" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A93" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C93" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A94" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C94" s="4">
+        <v>1</v>
+      </c>
+      <c r="D94" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E94" s="3">
+        <v>1</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A95" s="4"/>
+      <c r="B95" s="4"/>
+      <c r="C95" s="5"/>
+    </row>
+    <row r="96" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A96" s="4"/>
+      <c r="B96" s="4"/>
+      <c r="C96" s="5"/>
+    </row>
+    <row r="97" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A97" s="4"/>
+      <c r="B97" s="4"/>
+      <c r="C97" s="4"/>
+    </row>
+    <row r="98" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A98" s="4"/>
+      <c r="B98" s="4"/>
+      <c r="C98" s="6"/>
+    </row>
+    <row r="99" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A99" s="4"/>
+      <c r="B99" s="4"/>
+      <c r="C99" s="6"/>
+    </row>
+    <row r="100" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A100" s="4"/>
+      <c r="B100" s="4"/>
+      <c r="C100" s="1"/>
+    </row>
+    <row r="101" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A101" s="4"/>
+      <c r="B101" s="4"/>
+      <c r="C101" s="1"/>
+    </row>
+    <row r="102" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A102" s="4"/>
+      <c r="B102" s="4"/>
+      <c r="C102" s="6"/>
+    </row>
+    <row r="103" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A103" s="4"/>
+      <c r="B103" s="4"/>
+      <c r="C103" s="4"/>
+    </row>
+    <row r="104" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A104" s="4"/>
+      <c r="B104" s="4"/>
+      <c r="C104" s="5"/>
+    </row>
+    <row r="105" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A105" s="4"/>
+      <c r="B105" s="4"/>
+      <c r="C105" s="5"/>
+    </row>
+    <row r="106" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A106" s="4"/>
+      <c r="B106" s="4"/>
+      <c r="C106" s="4"/>
+    </row>
+    <row r="107" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A107" s="4"/>
+      <c r="B107" s="4"/>
+      <c r="C107" s="6"/>
+    </row>
+    <row r="108" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A108" s="4"/>
+      <c r="B108" s="4"/>
+      <c r="C108" s="6"/>
+    </row>
+    <row r="109" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A109" s="4"/>
+    </row>
+    <row r="110" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="111" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="112" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="113" ht="15.75" customHeight="1"/>
     <row r="114" ht="15.75" customHeight="1"/>
     <row r="115" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/WaveData.xlsx
+++ b/JsonConverter/ExcelFiles/WaveData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED8DC20-DF5C-4B9A-A680-8946C40F55C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4208F4FC-F8A4-44C7-B024-EC6AFBB750DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="720" windowWidth="28770" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="105" yWindow="0" windowWidth="31110" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="126">
   <si>
     <t>Id</t>
   </si>
@@ -2014,9 +2014,7 @@
       <c r="C49" s="4">
         <v>1</v>
       </c>
-      <c r="D49" s="10" t="s">
-        <v>81</v>
-      </c>
+      <c r="D49" s="10"/>
       <c r="E49" s="10">
         <v>1</v>
       </c>
@@ -2034,9 +2032,7 @@
       <c r="C50" s="5">
         <v>2</v>
       </c>
-      <c r="D50" s="10" t="s">
-        <v>81</v>
-      </c>
+      <c r="D50" s="10"/>
       <c r="E50" s="3">
         <v>3</v>
       </c>
@@ -2054,9 +2050,7 @@
       <c r="C51" s="5">
         <v>3</v>
       </c>
-      <c r="D51" s="10" t="s">
-        <v>81</v>
-      </c>
+      <c r="D51" s="10"/>
       <c r="E51" s="3">
         <v>5</v>
       </c>
@@ -2074,9 +2068,7 @@
       <c r="C52" s="4">
         <v>4</v>
       </c>
-      <c r="D52" s="10" t="s">
-        <v>81</v>
-      </c>
+      <c r="D52" s="10"/>
       <c r="E52" s="3">
         <v>7</v>
       </c>
@@ -2094,9 +2086,7 @@
       <c r="C53" s="6">
         <v>5</v>
       </c>
-      <c r="D53" s="10" t="s">
-        <v>81</v>
-      </c>
+      <c r="D53" s="10"/>
       <c r="E53" s="3">
         <v>9</v>
       </c>
@@ -2114,9 +2104,7 @@
       <c r="C54" s="6">
         <v>6</v>
       </c>
-      <c r="D54" s="10" t="s">
-        <v>81</v>
-      </c>
+      <c r="D54" s="10"/>
       <c r="E54" s="3">
         <v>11</v>
       </c>
@@ -2134,9 +2122,7 @@
       <c r="C55" s="1">
         <v>7</v>
       </c>
-      <c r="D55" s="10" t="s">
-        <v>81</v>
-      </c>
+      <c r="D55" s="10"/>
       <c r="E55" s="3">
         <v>13</v>
       </c>
@@ -2154,9 +2140,7 @@
       <c r="C56" s="1">
         <v>8</v>
       </c>
-      <c r="D56" s="10" t="s">
-        <v>81</v>
-      </c>
+      <c r="D56" s="10"/>
       <c r="E56" s="3">
         <v>15</v>
       </c>
@@ -2174,9 +2158,7 @@
       <c r="C57" s="6">
         <v>9</v>
       </c>
-      <c r="D57" s="10" t="s">
-        <v>81</v>
-      </c>
+      <c r="D57" s="10"/>
       <c r="E57" s="3">
         <v>17</v>
       </c>
@@ -2194,9 +2176,7 @@
       <c r="C58" s="4">
         <v>10</v>
       </c>
-      <c r="D58" s="10" t="s">
-        <v>81</v>
-      </c>
+      <c r="D58" s="10"/>
       <c r="E58" s="3">
         <v>19</v>
       </c>
@@ -2214,9 +2194,7 @@
       <c r="C59" s="5">
         <v>11</v>
       </c>
-      <c r="D59" s="10" t="s">
-        <v>81</v>
-      </c>
+      <c r="D59" s="10"/>
       <c r="E59" s="3">
         <v>21</v>
       </c>
@@ -2234,9 +2212,7 @@
       <c r="C60" s="5">
         <v>12</v>
       </c>
-      <c r="D60" s="10" t="s">
-        <v>81</v>
-      </c>
+      <c r="D60" s="10"/>
       <c r="E60" s="3">
         <v>23</v>
       </c>
@@ -2254,9 +2230,7 @@
       <c r="C61" s="4">
         <v>13</v>
       </c>
-      <c r="D61" s="10" t="s">
-        <v>81</v>
-      </c>
+      <c r="D61" s="10"/>
       <c r="E61" s="3">
         <v>25</v>
       </c>
@@ -2274,9 +2248,7 @@
       <c r="C62" s="6">
         <v>14</v>
       </c>
-      <c r="D62" s="10" t="s">
-        <v>81</v>
-      </c>
+      <c r="D62" s="10"/>
       <c r="E62" s="3">
         <v>27</v>
       </c>
@@ -2294,9 +2266,7 @@
       <c r="C63" s="6">
         <v>15</v>
       </c>
-      <c r="D63" s="10" t="s">
-        <v>81</v>
-      </c>
+      <c r="D63" s="10"/>
       <c r="E63" s="3">
         <v>29</v>
       </c>
@@ -2314,9 +2284,7 @@
       <c r="C64" s="4">
         <v>1</v>
       </c>
-      <c r="D64" s="10" t="s">
-        <v>82</v>
-      </c>
+      <c r="D64" s="10"/>
       <c r="E64" s="3">
         <v>1</v>
       </c>
@@ -2334,9 +2302,7 @@
       <c r="C65" s="5">
         <v>2</v>
       </c>
-      <c r="D65" s="10" t="s">
-        <v>82</v>
-      </c>
+      <c r="D65" s="10"/>
       <c r="E65" s="3">
         <v>1</v>
       </c>

--- a/JsonConverter/ExcelFiles/WaveData.xlsx
+++ b/JsonConverter/ExcelFiles/WaveData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4208F4FC-F8A4-44C7-B024-EC6AFBB750DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3C4D5D2-3449-461B-B2BA-7E568E67D09C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="105" yWindow="0" windowWidth="31110" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="720" windowWidth="31110" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="126">
   <si>
     <t>Id</t>
   </si>
@@ -2014,9 +2014,11 @@
       <c r="C49" s="4">
         <v>1</v>
       </c>
-      <c r="D49" s="10"/>
+      <c r="D49" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="E49" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F49" s="10">
         <v>0.5</v>

--- a/JsonConverter/ExcelFiles/WaveData.xlsx
+++ b/JsonConverter/ExcelFiles/WaveData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3C4D5D2-3449-461B-B2BA-7E568E67D09C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1923ABAE-497E-414D-B176-76001404050C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="720" windowWidth="31110" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5745" yWindow="465" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="127">
   <si>
     <t>Id</t>
   </si>
@@ -469,6 +469,21 @@
   </si>
   <si>
     <t>Chapter_Earth_7</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>nemy_agent_01</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -589,7 +604,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -611,6 +626,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2014,14 +2030,14 @@
       <c r="C49" s="4">
         <v>1</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>91</v>
+      <c r="D49" s="11" t="s">
+        <v>126</v>
       </c>
       <c r="E49" s="10">
+        <v>1</v>
+      </c>
+      <c r="F49" s="10">
         <v>5</v>
-      </c>
-      <c r="F49" s="10">
-        <v>0.5</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" customHeight="1">
@@ -2034,12 +2050,14 @@
       <c r="C50" s="5">
         <v>2</v>
       </c>
-      <c r="D50" s="10"/>
+      <c r="D50" s="11" t="s">
+        <v>126</v>
+      </c>
       <c r="E50" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F50" s="10">
-        <v>0.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" customHeight="1">
@@ -2052,12 +2070,14 @@
       <c r="C51" s="5">
         <v>3</v>
       </c>
-      <c r="D51" s="10"/>
+      <c r="D51" s="11" t="s">
+        <v>126</v>
+      </c>
       <c r="E51" s="3">
+        <v>1</v>
+      </c>
+      <c r="F51" s="10">
         <v>5</v>
-      </c>
-      <c r="F51" s="10">
-        <v>0.5</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" customHeight="1">
@@ -2070,12 +2090,14 @@
       <c r="C52" s="4">
         <v>4</v>
       </c>
-      <c r="D52" s="10"/>
+      <c r="D52" s="11" t="s">
+        <v>126</v>
+      </c>
       <c r="E52" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F52" s="10">
-        <v>0.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" customHeight="1">
@@ -2088,12 +2110,14 @@
       <c r="C53" s="6">
         <v>5</v>
       </c>
-      <c r="D53" s="10"/>
+      <c r="D53" s="11" t="s">
+        <v>126</v>
+      </c>
       <c r="E53" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F53" s="10">
-        <v>0.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" customHeight="1">
@@ -2106,12 +2130,14 @@
       <c r="C54" s="6">
         <v>6</v>
       </c>
-      <c r="D54" s="10"/>
+      <c r="D54" s="11" t="s">
+        <v>126</v>
+      </c>
       <c r="E54" s="3">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F54" s="10">
-        <v>0.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" customHeight="1">
@@ -2124,12 +2150,14 @@
       <c r="C55" s="1">
         <v>7</v>
       </c>
-      <c r="D55" s="10"/>
+      <c r="D55" s="11" t="s">
+        <v>126</v>
+      </c>
       <c r="E55" s="3">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F55" s="10">
-        <v>0.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" customHeight="1">
@@ -2142,12 +2170,14 @@
       <c r="C56" s="1">
         <v>8</v>
       </c>
-      <c r="D56" s="10"/>
+      <c r="D56" s="11" t="s">
+        <v>126</v>
+      </c>
       <c r="E56" s="3">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F56" s="10">
-        <v>0.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" customHeight="1">
@@ -2160,12 +2190,14 @@
       <c r="C57" s="6">
         <v>9</v>
       </c>
-      <c r="D57" s="10"/>
+      <c r="D57" s="11" t="s">
+        <v>126</v>
+      </c>
       <c r="E57" s="3">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F57" s="10">
-        <v>0.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" customHeight="1">
@@ -2178,12 +2210,14 @@
       <c r="C58" s="4">
         <v>10</v>
       </c>
-      <c r="D58" s="10"/>
+      <c r="D58" s="11" t="s">
+        <v>126</v>
+      </c>
       <c r="E58" s="3">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F58" s="10">
-        <v>0.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.75" customHeight="1">
@@ -2196,12 +2230,14 @@
       <c r="C59" s="5">
         <v>11</v>
       </c>
-      <c r="D59" s="10"/>
+      <c r="D59" s="11" t="s">
+        <v>126</v>
+      </c>
       <c r="E59" s="3">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F59" s="10">
-        <v>0.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" customHeight="1">
@@ -2214,12 +2250,14 @@
       <c r="C60" s="5">
         <v>12</v>
       </c>
-      <c r="D60" s="10"/>
+      <c r="D60" s="11" t="s">
+        <v>126</v>
+      </c>
       <c r="E60" s="3">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F60" s="10">
-        <v>0.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.75" customHeight="1">
@@ -2232,12 +2270,14 @@
       <c r="C61" s="4">
         <v>13</v>
       </c>
-      <c r="D61" s="10"/>
+      <c r="D61" s="11" t="s">
+        <v>126</v>
+      </c>
       <c r="E61" s="3">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F61" s="10">
-        <v>0.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.75" customHeight="1">
@@ -2250,12 +2290,14 @@
       <c r="C62" s="6">
         <v>14</v>
       </c>
-      <c r="D62" s="10"/>
+      <c r="D62" s="11" t="s">
+        <v>126</v>
+      </c>
       <c r="E62" s="3">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F62" s="10">
-        <v>0.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.75" customHeight="1">
@@ -2268,12 +2310,14 @@
       <c r="C63" s="6">
         <v>15</v>
       </c>
-      <c r="D63" s="10"/>
+      <c r="D63" s="11" t="s">
+        <v>126</v>
+      </c>
       <c r="E63" s="3">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F63" s="10">
-        <v>0.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15.75" customHeight="1">
@@ -2286,7 +2330,9 @@
       <c r="C64" s="4">
         <v>1</v>
       </c>
-      <c r="D64" s="10"/>
+      <c r="D64" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="E64" s="3">
         <v>1</v>
       </c>

--- a/JsonConverter/ExcelFiles/WaveData.xlsx
+++ b/JsonConverter/ExcelFiles/WaveData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1923ABAE-497E-414D-B176-76001404050C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E18FE98E-52FC-4E2B-AB0E-BD0797F400B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5745" yWindow="465" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8325" yWindow="270" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="132">
   <si>
     <t>Id</t>
   </si>
@@ -472,18 +472,27 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>e</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>nemy_agent_01</t>
-    </r>
+    <t>enemy_agent_01,enemy_agent_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_agent_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_agent_03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_agent_01,enemy_agent_03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_agent_02,enemy_agent_03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_agent_01,enemy_agent_02,enemy_agent_03</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -2031,10 +2040,10 @@
         <v>1</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E49" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F49" s="10">
         <v>5</v>
@@ -2051,7 +2060,7 @@
         <v>2</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E50" s="3">
         <v>1</v>
@@ -2071,7 +2080,7 @@
         <v>3</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E51" s="3">
         <v>1</v>
@@ -2094,7 +2103,7 @@
         <v>126</v>
       </c>
       <c r="E52" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F52" s="10">
         <v>5</v>
@@ -2111,10 +2120,10 @@
         <v>5</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E53" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F53" s="10">
         <v>5</v>
@@ -2131,10 +2140,10 @@
         <v>6</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E54" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F54" s="10">
         <v>5</v>
@@ -2151,10 +2160,10 @@
         <v>7</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E55" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F55" s="10">
         <v>5</v>
@@ -2171,10 +2180,10 @@
         <v>8</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E56" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F56" s="10">
         <v>5</v>
@@ -2191,10 +2200,10 @@
         <v>9</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E57" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F57" s="10">
         <v>5</v>
@@ -2211,10 +2220,10 @@
         <v>10</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E58" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F58" s="10">
         <v>5</v>
@@ -2231,10 +2240,10 @@
         <v>11</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E59" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F59" s="10">
         <v>5</v>
@@ -2251,10 +2260,10 @@
         <v>12</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E60" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F60" s="10">
         <v>5</v>
@@ -2271,7 +2280,7 @@
         <v>13</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E61" s="3">
         <v>15</v>
@@ -2291,7 +2300,7 @@
         <v>14</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E62" s="3">
         <v>15</v>
@@ -2311,7 +2320,7 @@
         <v>15</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E63" s="3">
         <v>15</v>

--- a/JsonConverter/ExcelFiles/WaveData.xlsx
+++ b/JsonConverter/ExcelFiles/WaveData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E18FE98E-52FC-4E2B-AB0E-BD0797F400B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3B56B5-D3B6-4179-89F7-5B87E0AC38A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8325" yWindow="270" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8955" yWindow="0" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="133">
   <si>
     <t>Id</t>
   </si>
@@ -493,6 +493,10 @@
   </si>
   <si>
     <t>enemy_agent_01,enemy_agent_02,enemy_agent_03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_subject_01,enemy_subject_02,enemy_subject_03,enemy_subject_04,enemy_subject_05</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1055,7 +1059,7 @@
   <cols>
     <col min="1" max="2" width="19.42578125" style="3" customWidth="1"/>
     <col min="3" max="3" width="19.5703125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="54.28515625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="82.7109375" style="3" customWidth="1"/>
     <col min="5" max="5" width="14.85546875" style="3" customWidth="1"/>
     <col min="6" max="6" width="13.85546875" style="3" customWidth="1"/>
     <col min="7" max="9" width="12.5703125" style="3"/>
@@ -2339,14 +2343,14 @@
       <c r="C64" s="4">
         <v>1</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>91</v>
+      <c r="D64" s="11" t="s">
+        <v>132</v>
       </c>
       <c r="E64" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F64" s="3">
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="15.75" customHeight="1">
@@ -2359,7 +2363,9 @@
       <c r="C65" s="5">
         <v>2</v>
       </c>
-      <c r="D65" s="10"/>
+      <c r="D65" s="11" t="s">
+        <v>132</v>
+      </c>
       <c r="E65" s="3">
         <v>1</v>
       </c>
@@ -2377,6 +2383,15 @@
       <c r="C66" s="5">
         <v>3</v>
       </c>
+      <c r="D66" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1</v>
+      </c>
+      <c r="F66" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="67" spans="1:6" ht="15.75" customHeight="1">
       <c r="A67" s="4" t="s">
@@ -2388,6 +2403,15 @@
       <c r="C67" s="4">
         <v>4</v>
       </c>
+      <c r="D67" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E67" s="3">
+        <v>1</v>
+      </c>
+      <c r="F67" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="68" spans="1:6" ht="15.75" customHeight="1">
       <c r="A68" s="4" t="s">
@@ -2399,6 +2423,15 @@
       <c r="C68" s="6">
         <v>5</v>
       </c>
+      <c r="D68" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E68" s="3">
+        <v>1</v>
+      </c>
+      <c r="F68" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="69" spans="1:6" ht="15.75" customHeight="1">
       <c r="A69" s="4" t="s">
@@ -2410,6 +2443,15 @@
       <c r="C69" s="6">
         <v>6</v>
       </c>
+      <c r="D69" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E69" s="3">
+        <v>1</v>
+      </c>
+      <c r="F69" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="70" spans="1:6" ht="15.75" customHeight="1">
       <c r="A70" s="4" t="s">
@@ -2421,6 +2463,15 @@
       <c r="C70" s="1">
         <v>7</v>
       </c>
+      <c r="D70" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E70" s="3">
+        <v>1</v>
+      </c>
+      <c r="F70" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="71" spans="1:6" ht="15.75" customHeight="1">
       <c r="A71" s="4" t="s">
@@ -2432,6 +2483,15 @@
       <c r="C71" s="1">
         <v>8</v>
       </c>
+      <c r="D71" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E71" s="3">
+        <v>1</v>
+      </c>
+      <c r="F71" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="72" spans="1:6" ht="15.75" customHeight="1">
       <c r="A72" s="4" t="s">
@@ -2443,6 +2503,15 @@
       <c r="C72" s="6">
         <v>9</v>
       </c>
+      <c r="D72" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1</v>
+      </c>
+      <c r="F72" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="73" spans="1:6" ht="15.75" customHeight="1">
       <c r="A73" s="4" t="s">
@@ -2454,6 +2523,15 @@
       <c r="C73" s="4">
         <v>10</v>
       </c>
+      <c r="D73" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E73" s="3">
+        <v>1</v>
+      </c>
+      <c r="F73" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="74" spans="1:6" ht="15.75" customHeight="1">
       <c r="A74" s="4" t="s">
@@ -2465,6 +2543,15 @@
       <c r="C74" s="5">
         <v>11</v>
       </c>
+      <c r="D74" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E74" s="3">
+        <v>1</v>
+      </c>
+      <c r="F74" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="75" spans="1:6" ht="15.75" customHeight="1">
       <c r="A75" s="4" t="s">
@@ -2476,6 +2563,15 @@
       <c r="C75" s="5">
         <v>12</v>
       </c>
+      <c r="D75" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E75" s="3">
+        <v>1</v>
+      </c>
+      <c r="F75" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="76" spans="1:6" ht="15.75" customHeight="1">
       <c r="A76" s="4" t="s">
@@ -2487,6 +2583,15 @@
       <c r="C76" s="4">
         <v>13</v>
       </c>
+      <c r="D76" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1</v>
+      </c>
+      <c r="F76" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="77" spans="1:6" ht="15.75" customHeight="1">
       <c r="A77" s="4" t="s">
@@ -2498,6 +2603,15 @@
       <c r="C77" s="6">
         <v>14</v>
       </c>
+      <c r="D77" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E77" s="3">
+        <v>1</v>
+      </c>
+      <c r="F77" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="78" spans="1:6" ht="15.75" customHeight="1">
       <c r="A78" s="4" t="s">
@@ -2508,6 +2622,15 @@
       </c>
       <c r="C78" s="6">
         <v>15</v>
+      </c>
+      <c r="D78" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E78" s="3">
+        <v>1</v>
+      </c>
+      <c r="F78" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/WaveData.xlsx
+++ b/JsonConverter/ExcelFiles/WaveData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3B56B5-D3B6-4179-89F7-5B87E0AC38A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F176EF4-723F-4449-8543-D5150770EA67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8955" yWindow="0" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7755" yWindow="210" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="134">
   <si>
     <t>Id</t>
   </si>
@@ -497,6 +497,10 @@
   </si>
   <si>
     <t>enemy_subject_01,enemy_subject_02,enemy_subject_03,enemy_subject_04,enemy_subject_05</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_type_01,enemy_type_02,enemy_type_03,enemy_type_04</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -2643,6 +2647,15 @@
       <c r="C79" s="4">
         <v>1</v>
       </c>
+      <c r="D79" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E79" s="3">
+        <v>10</v>
+      </c>
+      <c r="F79" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="80" spans="1:6" ht="15.75" customHeight="1">
       <c r="A80" s="4" t="s">
@@ -2654,6 +2667,15 @@
       <c r="C80" s="5">
         <v>2</v>
       </c>
+      <c r="D80" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E80" s="3">
+        <v>1</v>
+      </c>
+      <c r="F80" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="81" spans="1:6" ht="15.75" customHeight="1">
       <c r="A81" s="4" t="s">
@@ -2665,6 +2687,15 @@
       <c r="C81" s="5">
         <v>3</v>
       </c>
+      <c r="D81" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E81" s="3">
+        <v>1</v>
+      </c>
+      <c r="F81" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="82" spans="1:6" ht="15.75" customHeight="1">
       <c r="A82" s="4" t="s">
@@ -2676,6 +2707,15 @@
       <c r="C82" s="4">
         <v>4</v>
       </c>
+      <c r="D82" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E82" s="3">
+        <v>1</v>
+      </c>
+      <c r="F82" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="83" spans="1:6" ht="15.75" customHeight="1">
       <c r="A83" s="4" t="s">
@@ -2687,6 +2727,15 @@
       <c r="C83" s="6">
         <v>5</v>
       </c>
+      <c r="D83" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1</v>
+      </c>
+      <c r="F83" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="84" spans="1:6" ht="15.75" customHeight="1">
       <c r="A84" s="4" t="s">
@@ -2698,6 +2747,15 @@
       <c r="C84" s="6">
         <v>6</v>
       </c>
+      <c r="D84" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E84" s="3">
+        <v>1</v>
+      </c>
+      <c r="F84" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="85" spans="1:6" ht="15.75" customHeight="1">
       <c r="A85" s="4" t="s">
@@ -2709,6 +2767,15 @@
       <c r="C85" s="1">
         <v>7</v>
       </c>
+      <c r="D85" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E85" s="3">
+        <v>1</v>
+      </c>
+      <c r="F85" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="86" spans="1:6" ht="15.75" customHeight="1">
       <c r="A86" s="4" t="s">
@@ -2720,6 +2787,15 @@
       <c r="C86" s="1">
         <v>8</v>
       </c>
+      <c r="D86" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E86" s="3">
+        <v>1</v>
+      </c>
+      <c r="F86" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="87" spans="1:6" ht="15.75" customHeight="1">
       <c r="A87" s="4" t="s">
@@ -2731,6 +2807,15 @@
       <c r="C87" s="6">
         <v>9</v>
       </c>
+      <c r="D87" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E87" s="3">
+        <v>1</v>
+      </c>
+      <c r="F87" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="88" spans="1:6" ht="15.75" customHeight="1">
       <c r="A88" s="4" t="s">
@@ -2742,6 +2827,15 @@
       <c r="C88" s="4">
         <v>10</v>
       </c>
+      <c r="D88" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E88" s="3">
+        <v>1</v>
+      </c>
+      <c r="F88" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="89" spans="1:6" ht="15.75" customHeight="1">
       <c r="A89" s="4" t="s">
@@ -2753,6 +2847,15 @@
       <c r="C89" s="5">
         <v>11</v>
       </c>
+      <c r="D89" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1</v>
+      </c>
+      <c r="F89" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="90" spans="1:6" ht="15.75" customHeight="1">
       <c r="A90" s="4" t="s">
@@ -2764,6 +2867,15 @@
       <c r="C90" s="5">
         <v>12</v>
       </c>
+      <c r="D90" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E90" s="3">
+        <v>1</v>
+      </c>
+      <c r="F90" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="91" spans="1:6" ht="15.75" customHeight="1">
       <c r="A91" s="4" t="s">
@@ -2775,6 +2887,15 @@
       <c r="C91" s="4">
         <v>13</v>
       </c>
+      <c r="D91" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E91" s="3">
+        <v>1</v>
+      </c>
+      <c r="F91" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="92" spans="1:6" ht="15.75" customHeight="1">
       <c r="A92" s="4" t="s">
@@ -2786,6 +2907,15 @@
       <c r="C92" s="6">
         <v>14</v>
       </c>
+      <c r="D92" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E92" s="3">
+        <v>1</v>
+      </c>
+      <c r="F92" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="93" spans="1:6" ht="15.75" customHeight="1">
       <c r="A93" s="4" t="s">
@@ -2796,6 +2926,15 @@
       </c>
       <c r="C93" s="6">
         <v>15</v>
+      </c>
+      <c r="D93" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E93" s="3">
+        <v>1</v>
+      </c>
+      <c r="F93" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/WaveData.xlsx
+++ b/JsonConverter/ExcelFiles/WaveData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F176EF4-723F-4449-8543-D5150770EA67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20086922-8E24-45EF-A035-2D08CE48BE34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7755" yWindow="210" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6690" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="135">
   <si>
     <t>Id</t>
   </si>
@@ -501,6 +501,21 @@
   </si>
   <si>
     <t>enemy_type_01,enemy_type_02,enemy_type_03,enemy_type_04</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>nemy_boss_eclipse</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -621,7 +636,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -644,6 +659,7 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2947,14 +2963,14 @@
       <c r="C94" s="4">
         <v>1</v>
       </c>
-      <c r="D94" s="10" t="s">
-        <v>82</v>
+      <c r="D94" s="12" t="s">
+        <v>134</v>
       </c>
       <c r="E94" s="3">
         <v>1</v>
       </c>
       <c r="F94" s="3">
-        <v>0.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/WaveData.xlsx
+++ b/JsonConverter/ExcelFiles/WaveData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20086922-8E24-45EF-A035-2D08CE48BE34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1410B0D4-A64F-4F64-8BA1-5442FEB46877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6690" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="420" yWindow="450" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -1167,7 +1167,7 @@
         <v>82</v>
       </c>
       <c r="E4" s="10">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F4" s="10">
         <v>0.5</v>
@@ -1187,7 +1187,7 @@
         <v>30</v>
       </c>
       <c r="E5" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F5" s="10">
         <v>0.5</v>
@@ -1207,7 +1207,7 @@
         <v>30</v>
       </c>
       <c r="E6" s="3">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F6" s="10">
         <v>0.5</v>
@@ -1227,7 +1227,7 @@
         <v>30</v>
       </c>
       <c r="E7" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F7" s="10">
         <v>0.5</v>
@@ -1247,7 +1247,7 @@
         <v>30</v>
       </c>
       <c r="E8" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F8" s="10">
         <v>0.5</v>
@@ -1267,7 +1267,7 @@
         <v>89</v>
       </c>
       <c r="E9" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F9" s="10">
         <v>0.5</v>
@@ -1287,7 +1287,7 @@
         <v>89</v>
       </c>
       <c r="E10" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F10" s="10">
         <v>0.5</v>
@@ -1307,7 +1307,7 @@
         <v>89</v>
       </c>
       <c r="E11" s="3">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F11" s="10">
         <v>0.5</v>
@@ -1327,7 +1327,7 @@
         <v>89</v>
       </c>
       <c r="E12" s="3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F12" s="10">
         <v>0.5</v>
@@ -1347,7 +1347,7 @@
         <v>89</v>
       </c>
       <c r="E13" s="3">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F13" s="10">
         <v>0.5</v>
@@ -1367,7 +1367,7 @@
         <v>81</v>
       </c>
       <c r="E14" s="3">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="F14" s="10">
         <v>0.5</v>
@@ -1387,7 +1387,7 @@
         <v>81</v>
       </c>
       <c r="E15" s="3">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="F15" s="10">
         <v>0.5</v>
@@ -1407,7 +1407,7 @@
         <v>81</v>
       </c>
       <c r="E16" s="3">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="F16" s="10">
         <v>0.5</v>
@@ -1427,7 +1427,7 @@
         <v>81</v>
       </c>
       <c r="E17" s="3">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="F17" s="10">
         <v>0.5</v>
@@ -1447,7 +1447,7 @@
         <v>81</v>
       </c>
       <c r="E18" s="3">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="F18" s="10">
         <v>0.5</v>
@@ -1467,7 +1467,7 @@
         <v>90</v>
       </c>
       <c r="E19" s="10">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F19" s="10">
         <v>0.5</v>
@@ -1507,7 +1507,7 @@
         <v>91</v>
       </c>
       <c r="E21" s="3">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F21" s="10">
         <v>0.5</v>
@@ -1527,7 +1527,7 @@
         <v>91</v>
       </c>
       <c r="E22" s="3">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F22" s="10">
         <v>0.5</v>
@@ -1547,7 +1547,7 @@
         <v>83</v>
       </c>
       <c r="E23" s="3">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F23" s="10">
         <v>0.5</v>
@@ -1567,7 +1567,7 @@
         <v>90</v>
       </c>
       <c r="E24" s="3">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F24" s="10">
         <v>0.5</v>
@@ -1587,7 +1587,7 @@
         <v>90</v>
       </c>
       <c r="E25" s="3">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F25" s="10">
         <v>0.5</v>
@@ -1607,7 +1607,7 @@
         <v>91</v>
       </c>
       <c r="E26" s="3">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F26" s="10">
         <v>0.5</v>
@@ -1627,7 +1627,7 @@
         <v>91</v>
       </c>
       <c r="E27" s="3">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="F27" s="10">
         <v>0.5</v>
@@ -1647,7 +1647,7 @@
         <v>83</v>
       </c>
       <c r="E28" s="3">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="F28" s="10">
         <v>0.5</v>
@@ -1667,7 +1667,7 @@
         <v>90</v>
       </c>
       <c r="E29" s="3">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="F29" s="10">
         <v>0.5</v>
@@ -1687,7 +1687,7 @@
         <v>91</v>
       </c>
       <c r="E30" s="3">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F30" s="10">
         <v>0.5</v>
@@ -1707,7 +1707,7 @@
         <v>83</v>
       </c>
       <c r="E31" s="3">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="F31" s="10">
         <v>0.5</v>
@@ -1727,7 +1727,7 @@
         <v>83</v>
       </c>
       <c r="E32" s="3">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="F32" s="10">
         <v>0.5</v>
@@ -1747,7 +1747,7 @@
         <v>83</v>
       </c>
       <c r="E33" s="3">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="F33" s="10">
         <v>0.5</v>
@@ -1787,7 +1787,7 @@
         <v>87</v>
       </c>
       <c r="E35" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F35" s="10">
         <v>1</v>
@@ -1807,7 +1807,7 @@
         <v>88</v>
       </c>
       <c r="E36" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F36" s="10">
         <v>1</v>
@@ -1827,7 +1827,7 @@
         <v>85</v>
       </c>
       <c r="E37" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F37" s="10">
         <v>1.5</v>
@@ -1847,7 +1847,7 @@
         <v>85</v>
       </c>
       <c r="E38" s="3">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F38" s="10">
         <v>1.5</v>
@@ -1867,7 +1867,7 @@
         <v>85</v>
       </c>
       <c r="E39" s="3">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F39" s="10">
         <v>1.5</v>
@@ -1887,7 +1887,7 @@
         <v>85</v>
       </c>
       <c r="E40" s="3">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F40" s="10">
         <v>1.5</v>
@@ -1907,7 +1907,7 @@
         <v>85</v>
       </c>
       <c r="E41" s="3">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F41" s="10">
         <v>1.5</v>
@@ -1927,7 +1927,7 @@
         <v>85</v>
       </c>
       <c r="E42" s="3">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F42" s="10">
         <v>1.5</v>
@@ -1947,7 +1947,7 @@
         <v>86</v>
       </c>
       <c r="E43" s="3">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="F43" s="10">
         <v>2</v>
@@ -1967,7 +1967,7 @@
         <v>86</v>
       </c>
       <c r="E44" s="3">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="F44" s="10">
         <v>2</v>
@@ -1987,7 +1987,7 @@
         <v>86</v>
       </c>
       <c r="E45" s="3">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="F45" s="10">
         <v>2</v>
@@ -2007,7 +2007,7 @@
         <v>86</v>
       </c>
       <c r="E46" s="3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F46" s="10">
         <v>2</v>
@@ -2027,7 +2027,7 @@
         <v>86</v>
       </c>
       <c r="E47" s="3">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="F47" s="10">
         <v>2</v>
@@ -2047,7 +2047,7 @@
         <v>86</v>
       </c>
       <c r="E48" s="3">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F48" s="10">
         <v>2</v>
@@ -2070,7 +2070,7 @@
         <v>4</v>
       </c>
       <c r="F49" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" customHeight="1">
@@ -2087,10 +2087,10 @@
         <v>127</v>
       </c>
       <c r="E50" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F50" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" customHeight="1">
@@ -2107,10 +2107,10 @@
         <v>128</v>
       </c>
       <c r="E51" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F51" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" customHeight="1">
@@ -2127,10 +2127,10 @@
         <v>126</v>
       </c>
       <c r="E52" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F52" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" customHeight="1">
@@ -2147,10 +2147,10 @@
         <v>129</v>
       </c>
       <c r="E53" s="3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F53" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" customHeight="1">
@@ -2167,10 +2167,10 @@
         <v>130</v>
       </c>
       <c r="E54" s="3">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="F54" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" customHeight="1">
@@ -2187,10 +2187,10 @@
         <v>131</v>
       </c>
       <c r="E55" s="3">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="F55" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" customHeight="1">
@@ -2207,10 +2207,10 @@
         <v>131</v>
       </c>
       <c r="E56" s="3">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="F56" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" customHeight="1">
@@ -2227,10 +2227,10 @@
         <v>131</v>
       </c>
       <c r="E57" s="3">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="F57" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" customHeight="1">
@@ -2247,10 +2247,10 @@
         <v>131</v>
       </c>
       <c r="E58" s="3">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="F58" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.75" customHeight="1">
@@ -2267,10 +2267,10 @@
         <v>131</v>
       </c>
       <c r="E59" s="3">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="F59" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" customHeight="1">
@@ -2287,10 +2287,10 @@
         <v>131</v>
       </c>
       <c r="E60" s="3">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="F60" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.75" customHeight="1">
@@ -2307,10 +2307,10 @@
         <v>131</v>
       </c>
       <c r="E61" s="3">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="F61" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.75" customHeight="1">
@@ -2327,10 +2327,10 @@
         <v>131</v>
       </c>
       <c r="E62" s="3">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="F62" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.75" customHeight="1">
@@ -2347,10 +2347,10 @@
         <v>131</v>
       </c>
       <c r="E63" s="3">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="F63" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15.75" customHeight="1">
@@ -2366,11 +2366,11 @@
       <c r="D64" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="E64" s="3">
+      <c r="E64" s="10">
         <v>10</v>
       </c>
       <c r="F64" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="15.75" customHeight="1">
@@ -2387,10 +2387,10 @@
         <v>132</v>
       </c>
       <c r="E65" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F65" s="3">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="15.75" customHeight="1">
@@ -2407,10 +2407,10 @@
         <v>132</v>
       </c>
       <c r="E66" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F66" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="15.75" customHeight="1">
@@ -2427,10 +2427,10 @@
         <v>132</v>
       </c>
       <c r="E67" s="3">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F67" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="15.75" customHeight="1">
@@ -2447,10 +2447,10 @@
         <v>132</v>
       </c>
       <c r="E68" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F68" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="15.75" customHeight="1">
@@ -2467,10 +2467,10 @@
         <v>132</v>
       </c>
       <c r="E69" s="3">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="F69" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="15.75" customHeight="1">
@@ -2487,10 +2487,10 @@
         <v>132</v>
       </c>
       <c r="E70" s="3">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="F70" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15.75" customHeight="1">
@@ -2507,10 +2507,10 @@
         <v>132</v>
       </c>
       <c r="E71" s="3">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="F71" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="15.75" customHeight="1">
@@ -2527,10 +2527,10 @@
         <v>132</v>
       </c>
       <c r="E72" s="3">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="F72" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15.75" customHeight="1">
@@ -2547,10 +2547,10 @@
         <v>132</v>
       </c>
       <c r="E73" s="3">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="F73" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="15.75" customHeight="1">
@@ -2567,10 +2567,10 @@
         <v>132</v>
       </c>
       <c r="E74" s="3">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="F74" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="15.75" customHeight="1">
@@ -2587,10 +2587,10 @@
         <v>132</v>
       </c>
       <c r="E75" s="3">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="F75" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="15.75" customHeight="1">
@@ -2607,10 +2607,10 @@
         <v>132</v>
       </c>
       <c r="E76" s="3">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="F76" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="15.75" customHeight="1">
@@ -2627,10 +2627,10 @@
         <v>132</v>
       </c>
       <c r="E77" s="3">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="F77" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="15.75" customHeight="1">
@@ -2647,10 +2647,10 @@
         <v>132</v>
       </c>
       <c r="E78" s="3">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="F78" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="15.75" customHeight="1">
@@ -2666,11 +2666,11 @@
       <c r="D79" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="E79" s="3">
-        <v>10</v>
+      <c r="E79" s="10">
+        <v>11</v>
       </c>
       <c r="F79" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="15.75" customHeight="1">
@@ -2687,10 +2687,10 @@
         <v>133</v>
       </c>
       <c r="E80" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F80" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="15.75" customHeight="1">
@@ -2707,10 +2707,10 @@
         <v>133</v>
       </c>
       <c r="E81" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="F81" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="15.75" customHeight="1">
@@ -2727,10 +2727,10 @@
         <v>133</v>
       </c>
       <c r="E82" s="3">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="F82" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="15.75" customHeight="1">
@@ -2747,10 +2747,10 @@
         <v>133</v>
       </c>
       <c r="E83" s="3">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="F83" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="15.75" customHeight="1">
@@ -2767,10 +2767,10 @@
         <v>133</v>
       </c>
       <c r="E84" s="3">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="F84" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="15.75" customHeight="1">
@@ -2787,10 +2787,10 @@
         <v>133</v>
       </c>
       <c r="E85" s="3">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F85" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="15.75" customHeight="1">
@@ -2807,10 +2807,10 @@
         <v>133</v>
       </c>
       <c r="E86" s="3">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="F86" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="15.75" customHeight="1">
@@ -2827,10 +2827,10 @@
         <v>133</v>
       </c>
       <c r="E87" s="3">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="F87" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="15.75" customHeight="1">
@@ -2847,10 +2847,10 @@
         <v>133</v>
       </c>
       <c r="E88" s="3">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="F88" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="15.75" customHeight="1">
@@ -2867,10 +2867,10 @@
         <v>133</v>
       </c>
       <c r="E89" s="3">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="F89" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="15.75" customHeight="1">
@@ -2887,10 +2887,10 @@
         <v>133</v>
       </c>
       <c r="E90" s="3">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="F90" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="15.75" customHeight="1">
@@ -2907,10 +2907,10 @@
         <v>133</v>
       </c>
       <c r="E91" s="3">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="F91" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="15.75" customHeight="1">
@@ -2927,10 +2927,10 @@
         <v>133</v>
       </c>
       <c r="E92" s="3">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="F92" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="15.75" customHeight="1">
@@ -2947,10 +2947,10 @@
         <v>133</v>
       </c>
       <c r="E93" s="3">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="F93" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/WaveData.xlsx
+++ b/JsonConverter/ExcelFiles/WaveData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1410B0D4-A64F-4F64-8BA1-5442FEB46877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2820B9B3-240B-45A4-86E6-02C8B0637278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="420" yWindow="450" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3345" yWindow="765" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -1767,10 +1767,10 @@
         <v>84</v>
       </c>
       <c r="E34" s="10">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F34" s="10">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" customHeight="1">
@@ -1787,10 +1787,10 @@
         <v>87</v>
       </c>
       <c r="E35" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F35" s="10">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1">
@@ -1807,10 +1807,10 @@
         <v>88</v>
       </c>
       <c r="E36" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F36" s="10">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" customHeight="1">
@@ -1827,10 +1827,10 @@
         <v>85</v>
       </c>
       <c r="E37" s="3">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F37" s="10">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" customHeight="1">
@@ -1847,10 +1847,10 @@
         <v>85</v>
       </c>
       <c r="E38" s="3">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F38" s="10">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" customHeight="1">
@@ -1867,10 +1867,10 @@
         <v>85</v>
       </c>
       <c r="E39" s="3">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F39" s="10">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" customHeight="1">
@@ -1887,10 +1887,10 @@
         <v>85</v>
       </c>
       <c r="E40" s="3">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F40" s="10">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" customHeight="1">
@@ -1907,10 +1907,10 @@
         <v>85</v>
       </c>
       <c r="E41" s="3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F41" s="10">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" customHeight="1">
@@ -1927,10 +1927,10 @@
         <v>85</v>
       </c>
       <c r="E42" s="3">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="F42" s="10">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.75" customHeight="1">
@@ -1947,10 +1947,10 @@
         <v>86</v>
       </c>
       <c r="E43" s="3">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="F43" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" customHeight="1">
@@ -1967,10 +1967,10 @@
         <v>86</v>
       </c>
       <c r="E44" s="3">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="F44" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" customHeight="1">
@@ -1987,10 +1987,10 @@
         <v>86</v>
       </c>
       <c r="E45" s="3">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="F45" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" customHeight="1">
@@ -2007,10 +2007,10 @@
         <v>86</v>
       </c>
       <c r="E46" s="3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F46" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" customHeight="1">
@@ -2027,10 +2027,10 @@
         <v>86</v>
       </c>
       <c r="E47" s="3">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F47" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" customHeight="1">
@@ -2047,10 +2047,10 @@
         <v>86</v>
       </c>
       <c r="E48" s="3">
-        <v>75</v>
+        <v>700</v>
       </c>
       <c r="F48" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" customHeight="1">
@@ -2067,10 +2067,10 @@
         <v>129</v>
       </c>
       <c r="E49" s="10">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F49" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" customHeight="1">
@@ -2087,10 +2087,10 @@
         <v>127</v>
       </c>
       <c r="E50" s="3">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F50" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" customHeight="1">
@@ -2107,10 +2107,10 @@
         <v>128</v>
       </c>
       <c r="E51" s="3">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F51" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" customHeight="1">
@@ -2127,10 +2127,10 @@
         <v>126</v>
       </c>
       <c r="E52" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F52" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" customHeight="1">
@@ -2147,10 +2147,10 @@
         <v>129</v>
       </c>
       <c r="E53" s="3">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F53" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" customHeight="1">
@@ -2167,10 +2167,10 @@
         <v>130</v>
       </c>
       <c r="E54" s="3">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F54" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" customHeight="1">
@@ -2187,10 +2187,10 @@
         <v>131</v>
       </c>
       <c r="E55" s="3">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F55" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" customHeight="1">
@@ -2207,10 +2207,10 @@
         <v>131</v>
       </c>
       <c r="E56" s="3">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F56" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" customHeight="1">
@@ -2227,10 +2227,10 @@
         <v>131</v>
       </c>
       <c r="E57" s="3">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="F57" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" customHeight="1">
@@ -2247,10 +2247,10 @@
         <v>131</v>
       </c>
       <c r="E58" s="3">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F58" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.75" customHeight="1">
@@ -2267,10 +2267,10 @@
         <v>131</v>
       </c>
       <c r="E59" s="3">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F59" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" customHeight="1">
@@ -2287,10 +2287,10 @@
         <v>131</v>
       </c>
       <c r="E60" s="3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F60" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.75" customHeight="1">
@@ -2307,10 +2307,10 @@
         <v>131</v>
       </c>
       <c r="E61" s="3">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="F61" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.75" customHeight="1">
@@ -2327,10 +2327,10 @@
         <v>131</v>
       </c>
       <c r="E62" s="3">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="F62" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.75" customHeight="1">
@@ -2347,10 +2347,10 @@
         <v>131</v>
       </c>
       <c r="E63" s="3">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="F63" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15.75" customHeight="1">
@@ -2367,10 +2367,10 @@
         <v>132</v>
       </c>
       <c r="E64" s="10">
-        <v>10</v>
-      </c>
-      <c r="F64" s="3">
-        <v>2</v>
+        <v>20</v>
+      </c>
+      <c r="F64" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="15.75" customHeight="1">
@@ -2387,10 +2387,10 @@
         <v>132</v>
       </c>
       <c r="E65" s="3">
-        <v>13</v>
-      </c>
-      <c r="F65" s="3">
-        <v>2</v>
+        <v>25</v>
+      </c>
+      <c r="F65" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="15.75" customHeight="1">
@@ -2407,10 +2407,10 @@
         <v>132</v>
       </c>
       <c r="E66" s="3">
-        <v>15</v>
-      </c>
-      <c r="F66" s="3">
-        <v>2</v>
+        <v>35</v>
+      </c>
+      <c r="F66" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="15.75" customHeight="1">
@@ -2427,10 +2427,10 @@
         <v>132</v>
       </c>
       <c r="E67" s="3">
-        <v>21</v>
-      </c>
-      <c r="F67" s="3">
-        <v>2</v>
+        <v>45</v>
+      </c>
+      <c r="F67" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="15.75" customHeight="1">
@@ -2447,10 +2447,10 @@
         <v>132</v>
       </c>
       <c r="E68" s="3">
-        <v>27</v>
-      </c>
-      <c r="F68" s="3">
-        <v>2</v>
+        <v>50</v>
+      </c>
+      <c r="F68" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="15.75" customHeight="1">
@@ -2467,10 +2467,10 @@
         <v>132</v>
       </c>
       <c r="E69" s="3">
-        <v>33</v>
-      </c>
-      <c r="F69" s="3">
-        <v>2</v>
+        <v>60</v>
+      </c>
+      <c r="F69" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="15.75" customHeight="1">
@@ -2487,10 +2487,10 @@
         <v>132</v>
       </c>
       <c r="E70" s="3">
-        <v>40</v>
-      </c>
-      <c r="F70" s="3">
-        <v>2</v>
+        <v>65</v>
+      </c>
+      <c r="F70" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15.75" customHeight="1">
@@ -2507,10 +2507,10 @@
         <v>132</v>
       </c>
       <c r="E71" s="3">
-        <v>48</v>
-      </c>
-      <c r="F71" s="3">
-        <v>2</v>
+        <v>70</v>
+      </c>
+      <c r="F71" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="15.75" customHeight="1">
@@ -2527,10 +2527,10 @@
         <v>132</v>
       </c>
       <c r="E72" s="3">
-        <v>55</v>
-      </c>
-      <c r="F72" s="3">
-        <v>2</v>
+        <v>80</v>
+      </c>
+      <c r="F72" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15.75" customHeight="1">
@@ -2547,10 +2547,10 @@
         <v>132</v>
       </c>
       <c r="E73" s="3">
-        <v>64</v>
-      </c>
-      <c r="F73" s="3">
-        <v>2</v>
+        <v>88</v>
+      </c>
+      <c r="F73" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="15.75" customHeight="1">
@@ -2567,10 +2567,10 @@
         <v>132</v>
       </c>
       <c r="E74" s="3">
-        <v>75</v>
-      </c>
-      <c r="F74" s="3">
-        <v>2</v>
+        <v>92</v>
+      </c>
+      <c r="F74" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="15.75" customHeight="1">
@@ -2587,10 +2587,10 @@
         <v>132</v>
       </c>
       <c r="E75" s="3">
-        <v>84</v>
-      </c>
-      <c r="F75" s="3">
-        <v>2</v>
+        <v>98</v>
+      </c>
+      <c r="F75" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="15.75" customHeight="1">
@@ -2607,10 +2607,10 @@
         <v>132</v>
       </c>
       <c r="E76" s="3">
-        <v>94</v>
-      </c>
-      <c r="F76" s="3">
-        <v>2</v>
+        <v>100</v>
+      </c>
+      <c r="F76" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="15.75" customHeight="1">
@@ -2629,8 +2629,8 @@
       <c r="E77" s="3">
         <v>104</v>
       </c>
-      <c r="F77" s="3">
-        <v>2</v>
+      <c r="F77" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="15.75" customHeight="1">
@@ -2649,8 +2649,8 @@
       <c r="E78" s="3">
         <v>116</v>
       </c>
-      <c r="F78" s="3">
-        <v>2</v>
+      <c r="F78" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="15.75" customHeight="1">
@@ -2667,10 +2667,10 @@
         <v>133</v>
       </c>
       <c r="E79" s="10">
-        <v>11</v>
-      </c>
-      <c r="F79" s="3">
-        <v>2</v>
+        <v>20</v>
+      </c>
+      <c r="F79" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="15.75" customHeight="1">
@@ -2687,10 +2687,10 @@
         <v>133</v>
       </c>
       <c r="E80" s="3">
-        <v>13</v>
-      </c>
-      <c r="F80" s="3">
-        <v>2</v>
+        <v>25</v>
+      </c>
+      <c r="F80" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="15.75" customHeight="1">
@@ -2707,10 +2707,10 @@
         <v>133</v>
       </c>
       <c r="E81" s="3">
-        <v>17</v>
-      </c>
-      <c r="F81" s="3">
-        <v>2</v>
+        <v>30</v>
+      </c>
+      <c r="F81" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="15.75" customHeight="1">
@@ -2727,10 +2727,10 @@
         <v>133</v>
       </c>
       <c r="E82" s="3">
-        <v>22</v>
-      </c>
-      <c r="F82" s="3">
-        <v>2</v>
+        <v>35</v>
+      </c>
+      <c r="F82" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="15.75" customHeight="1">
@@ -2747,10 +2747,10 @@
         <v>133</v>
       </c>
       <c r="E83" s="3">
-        <v>29</v>
-      </c>
-      <c r="F83" s="3">
-        <v>2</v>
+        <v>40</v>
+      </c>
+      <c r="F83" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="15.75" customHeight="1">
@@ -2767,10 +2767,10 @@
         <v>133</v>
       </c>
       <c r="E84" s="3">
-        <v>37</v>
-      </c>
-      <c r="F84" s="3">
-        <v>2</v>
+        <v>45</v>
+      </c>
+      <c r="F84" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="15.75" customHeight="1">
@@ -2787,10 +2787,10 @@
         <v>133</v>
       </c>
       <c r="E85" s="3">
-        <v>45</v>
-      </c>
-      <c r="F85" s="3">
-        <v>2</v>
+        <v>50</v>
+      </c>
+      <c r="F85" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="15.75" customHeight="1">
@@ -2809,8 +2809,8 @@
       <c r="E86" s="3">
         <v>54</v>
       </c>
-      <c r="F86" s="3">
-        <v>2</v>
+      <c r="F86" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="15.75" customHeight="1">
@@ -2829,8 +2829,8 @@
       <c r="E87" s="3">
         <v>63</v>
       </c>
-      <c r="F87" s="3">
-        <v>2</v>
+      <c r="F87" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="15.75" customHeight="1">
@@ -2849,8 +2849,8 @@
       <c r="E88" s="3">
         <v>72</v>
       </c>
-      <c r="F88" s="3">
-        <v>2</v>
+      <c r="F88" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="15.75" customHeight="1">
@@ -2869,8 +2869,8 @@
       <c r="E89" s="3">
         <v>84</v>
       </c>
-      <c r="F89" s="3">
-        <v>2</v>
+      <c r="F89" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="15.75" customHeight="1">
@@ -2889,8 +2889,8 @@
       <c r="E90" s="3">
         <v>95</v>
       </c>
-      <c r="F90" s="3">
-        <v>2</v>
+      <c r="F90" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="15.75" customHeight="1">
@@ -2909,8 +2909,8 @@
       <c r="E91" s="3">
         <v>107</v>
       </c>
-      <c r="F91" s="3">
-        <v>2</v>
+      <c r="F91" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="15.75" customHeight="1">
@@ -2929,8 +2929,8 @@
       <c r="E92" s="3">
         <v>119</v>
       </c>
-      <c r="F92" s="3">
-        <v>2</v>
+      <c r="F92" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="15.75" customHeight="1">
@@ -2949,8 +2949,8 @@
       <c r="E93" s="3">
         <v>132</v>
       </c>
-      <c r="F93" s="3">
-        <v>2</v>
+      <c r="F93" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/WaveData.xlsx
+++ b/JsonConverter/ExcelFiles/WaveData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2820B9B3-240B-45A4-86E6-02C8B0637278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E3A8FB-0EDC-4DD8-901A-712BC872E206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3345" yWindow="765" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="720" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -2047,7 +2047,7 @@
         <v>86</v>
       </c>
       <c r="E48" s="3">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="F48" s="10">
         <v>0.5</v>
